--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -17599,6 +17599,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="750">
+      <c r="A750" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B750" t="n">
+        <v>39850</v>
+      </c>
+      <c r="C750" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D750" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="E750" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F750" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="G750" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -17622,6 +17622,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="751">
+      <c r="A751" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B751" t="n">
+        <v>61880</v>
+      </c>
+      <c r="C751" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="D751" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E751" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="F751" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="G751" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -17645,6 +17645,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="752">
+      <c r="A752" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B752" t="n">
+        <v>5067</v>
+      </c>
+      <c r="C752" t="n">
+        <v>4.17999982833862</v>
+      </c>
+      <c r="D752" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="E752" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="F752" t="n">
+        <v>4.17999982833862</v>
+      </c>
+      <c r="G752" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -17668,6 +17668,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="753">
+      <c r="A753" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B753" t="n">
+        <v>3108</v>
+      </c>
+      <c r="C753" t="n">
+        <v>4.26999998092651</v>
+      </c>
+      <c r="D753" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="E753" t="n">
+        <v>4.26999998092651</v>
+      </c>
+      <c r="F753" t="n">
+        <v>4.13000011444092</v>
+      </c>
+      <c r="G753" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -17509,19 +17509,19 @@
     </row>
     <row r="746">
       <c r="A746" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B746" t="n">
-        <v>10</v>
+        <v>1240</v>
       </c>
       <c r="C746" t="n">
-        <v>4.15000009536743</v>
+        <v>4.19000005722046</v>
       </c>
       <c r="D746" t="n">
         <v>4.15000009536743</v>
       </c>
       <c r="E746" t="n">
-        <v>4.15000009536743</v>
+        <v>4.19000005722046</v>
       </c>
       <c r="F746" t="n">
         <v>4.15000009536743</v>
@@ -17532,22 +17532,22 @@
     </row>
     <row r="747">
       <c r="A747" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B747" t="n">
-        <v>592</v>
+        <v>10</v>
       </c>
       <c r="C747" t="n">
-        <v>4.28999996185303</v>
+        <v>4.15000009536743</v>
       </c>
       <c r="D747" t="n">
-        <v>4.1100001335144</v>
+        <v>4.15000009536743</v>
       </c>
       <c r="E747" t="n">
-        <v>4.1100001335144</v>
+        <v>4.15000009536743</v>
       </c>
       <c r="F747" t="n">
-        <v>4.23000001907349</v>
+        <v>4.15000009536743</v>
       </c>
       <c r="G747" t="s">
         <v>7</v>
@@ -17555,22 +17555,22 @@
     </row>
     <row r="748">
       <c r="A748" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B748" t="n">
-        <v>1200</v>
+        <v>592</v>
       </c>
       <c r="C748" t="n">
-        <v>4.19999980926514</v>
+        <v>4.28999996185303</v>
       </c>
       <c r="D748" t="n">
-        <v>4.09999990463257</v>
+        <v>4.1100001335144</v>
       </c>
       <c r="E748" t="n">
         <v>4.1100001335144</v>
       </c>
       <c r="F748" t="n">
-        <v>4.19999980926514</v>
+        <v>4.23000001907349</v>
       </c>
       <c r="G748" t="s">
         <v>7</v>
@@ -17578,22 +17578,22 @@
     </row>
     <row r="749">
       <c r="A749" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B749" t="n">
-        <v>89393</v>
+        <v>1200</v>
       </c>
       <c r="C749" t="n">
-        <v>4.30000019073486</v>
+        <v>4.19999980926514</v>
       </c>
       <c r="D749" t="n">
-        <v>4.07000017166138</v>
+        <v>4.09999990463257</v>
       </c>
       <c r="E749" t="n">
         <v>4.1100001335144</v>
       </c>
       <c r="F749" t="n">
-        <v>4.30000019073486</v>
+        <v>4.19999980926514</v>
       </c>
       <c r="G749" t="s">
         <v>7</v>
@@ -17601,22 +17601,22 @@
     </row>
     <row r="750">
       <c r="A750" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B750" t="n">
-        <v>39850</v>
+        <v>89393</v>
       </c>
       <c r="C750" t="n">
         <v>4.30000019073486</v>
       </c>
       <c r="D750" t="n">
-        <v>4.17000007629395</v>
+        <v>4.07000017166138</v>
       </c>
       <c r="E750" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="F750" t="n">
         <v>4.30000019073486</v>
-      </c>
-      <c r="F750" t="n">
-        <v>4.28000020980835</v>
       </c>
       <c r="G750" t="s">
         <v>7</v>
@@ -17624,22 +17624,22 @@
     </row>
     <row r="751">
       <c r="A751" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B751" t="n">
-        <v>61880</v>
+        <v>39850</v>
       </c>
       <c r="C751" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D751" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="E751" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F751" t="n">
         <v>4.28000020980835</v>
-      </c>
-      <c r="D751" t="n">
-        <v>3.90000009536743</v>
-      </c>
-      <c r="E751" t="n">
-        <v>4.28000020980835</v>
-      </c>
-      <c r="F751" t="n">
-        <v>4.23999977111816</v>
       </c>
       <c r="G751" t="s">
         <v>7</v>
@@ -17647,22 +17647,22 @@
     </row>
     <row r="752">
       <c r="A752" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B752" t="n">
-        <v>5067</v>
+        <v>61880</v>
       </c>
       <c r="C752" t="n">
-        <v>4.17999982833862</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="D752" t="n">
-        <v>4.09999990463257</v>
+        <v>3.90000009536743</v>
       </c>
       <c r="E752" t="n">
-        <v>4.09999990463257</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="F752" t="n">
-        <v>4.17999982833862</v>
+        <v>4.23999977111816</v>
       </c>
       <c r="G752" t="s">
         <v>7</v>
@@ -17670,24 +17670,47 @@
     </row>
     <row r="753">
       <c r="A753" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B753" t="n">
-        <v>3108</v>
+        <v>5067</v>
       </c>
       <c r="C753" t="n">
-        <v>4.26999998092651</v>
+        <v>4.17999982833862</v>
       </c>
       <c r="D753" t="n">
         <v>4.09999990463257</v>
       </c>
       <c r="E753" t="n">
-        <v>4.26999998092651</v>
+        <v>4.09999990463257</v>
       </c>
       <c r="F753" t="n">
-        <v>4.13000011444092</v>
+        <v>4.17999982833862</v>
       </c>
       <c r="G753" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B754" t="n">
+        <v>5550</v>
+      </c>
+      <c r="C754" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="D754" t="n">
+        <v>4.07999992370605</v>
+      </c>
+      <c r="E754" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="F754" t="n">
+        <v>4.1399998664856</v>
+      </c>
+      <c r="G754" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -20031,6 +20031,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B757" t="n">
+        <v>3212</v>
+      </c>
+      <c r="C757" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="D757" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="E757" t="n">
+        <v>4.07999992370605</v>
+      </c>
+      <c r="F757" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="G757" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="H757" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G3" t="n">
-        <v>2.40923547744751</v>
+        <v>2.40923571586609</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46740627288818</v>
+        <v>2.46740651130676</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.47710132598877</v>
+        <v>2.47710156440735</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54011940956116</v>
+        <v>2.54011964797974</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4577112197876</v>
+        <v>2.45771145820618</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>2.40438795089722</v>
+        <v>2.4043881893158</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.37530279159546</v>
+        <v>2.37530303001404</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>2.30743718147278</v>
+        <v>2.3074369430542</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.37530279159546</v>
+        <v>2.37530303001404</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>2.56920528411865</v>
+        <v>2.56920504570007</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.54981470108032</v>
+        <v>2.5498149394989</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>2.54011940956116</v>
+        <v>2.54011964797974</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>2.62737584114075</v>
+        <v>2.62737560272217</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G61" t="n">
-        <v>2.53042435646057</v>
+        <v>2.53042459487915</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8115828037262</v>
+        <v>2.81158304214478</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.88914370536804</v>
+        <v>2.88914394378662</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.03457069396973</v>
+        <v>3.03457045555115</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G89" t="n">
-        <v>3.09274101257324</v>
+        <v>3.09274125099182</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.2187774181366</v>
+        <v>3.21877765655518</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.35450911521912</v>
+        <v>3.3545093536377</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>3.53871655464172</v>
+        <v>3.53871631622314</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.17030215263367</v>
+        <v>3.17030191421509</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G109" t="n">
-        <v>3.2187774181366</v>
+        <v>3.21877765655518</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>3.35450911521912</v>
+        <v>3.3545093536377</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>3.03457069396973</v>
+        <v>3.03457045555115</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G125" t="n">
-        <v>2.97639989852905</v>
+        <v>2.97639966011047</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>3.12182664871216</v>
+        <v>3.12182641029358</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>3.38359475135803</v>
+        <v>3.38359451293945</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.5</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39328980445862</v>
+        <v>3.39328956604004</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G141" t="n">
-        <v>3.20908236503601</v>
+        <v>3.20908260345459</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G144" t="n">
-        <v>3.49993562698364</v>
+        <v>3.49993586540222</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>3.77139902114868</v>
+        <v>3.77139925956726</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>3.53871655464172</v>
+        <v>3.53871631622314</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G167" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G169" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G179" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G184" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G191" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G192" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G195" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G216" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>3.96530151367188</v>
+        <v>3.9653012752533</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14950847625732</v>
+        <v>4.14950895309448</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G234" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G237" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G248" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>4.10103273391724</v>
+        <v>4.10103321075439</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G256" t="n">
-        <v>3.96530151367188</v>
+        <v>3.9653012752533</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>4.41127634048462</v>
+        <v>4.41127681732178</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G276" t="n">
-        <v>4.14950847625732</v>
+        <v>4.14950895309448</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>4.10103273391724</v>
+        <v>4.10103321075439</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.75200867652893</v>
+        <v>3.75200891494751</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.57749700546265</v>
+        <v>3.57749676704407</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G291" t="n">
-        <v>3.58719205856323</v>
+        <v>3.58719182014465</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G295" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.75</v>
       </c>
       <c r="G296" t="n">
-        <v>3.63566732406616</v>
+        <v>3.63566756248474</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G304" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G308" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.25</v>
       </c>
       <c r="G319" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.25</v>
       </c>
       <c r="G321" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.25</v>
       </c>
       <c r="G325" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>4.32402086257935</v>
+        <v>4.32402038574219</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G338" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>4.45005750656128</v>
+        <v>4.45005702972412</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>4.61487436294556</v>
+        <v>4.6148738861084</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G359" t="n">
-        <v>5.06084871292114</v>
+        <v>5.0608491897583</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>4.63426446914673</v>
+        <v>4.63426399230957</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>4.61487436294556</v>
+        <v>4.6148738861084</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>4.45005750656128</v>
+        <v>4.45005702972412</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G367" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>5.09962940216064</v>
+        <v>5.0996298789978</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>4.79908084869385</v>
+        <v>4.79908132553101</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.8004846572876</v>
+        <v>3.80048441886902</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>3.9459114074707</v>
+        <v>3.94591116905212</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G414" t="n">
-        <v>3.62597227096558</v>
+        <v>3.62597250938416</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.49993562698364</v>
+        <v>3.49993586540222</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G426" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.63566732406616</v>
+        <v>3.63566756248474</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G432" t="n">
-        <v>3.77139902114868</v>
+        <v>3.77139925956726</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>3.9071307182312</v>
+        <v>3.90713095664978</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G436" t="n">
-        <v>3.84896016120911</v>
+        <v>3.84895992279053</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.9459114074707</v>
+        <v>3.94591116905212</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G439" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -20054,6 +20054,32 @@
         <v>4.1100001335144</v>
       </c>
       <c r="H757" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B758" t="n">
+        <v>1401</v>
+      </c>
+      <c r="C758" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="D758" t="n">
+        <v>4.01000022888184</v>
+      </c>
+      <c r="E758" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="F758" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="G758" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="H758" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G3" t="n">
-        <v>2.40923571586609</v>
+        <v>2.40923547744751</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46740651130676</v>
+        <v>2.46740627288818</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.47710156440735</v>
+        <v>2.47710132598877</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54011964797974</v>
+        <v>2.54011940956116</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>2.45771145820618</v>
+        <v>2.4577112197876</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>2.4043881893158</v>
+        <v>2.40438795089722</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.37530303001404</v>
+        <v>2.37530279159546</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>2.3074369430542</v>
+        <v>2.30743718147278</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.37530303001404</v>
+        <v>2.37530279159546</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>2.56920504570007</v>
+        <v>2.56920528411865</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.5498149394989</v>
+        <v>2.54981470108032</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>2.54011964797974</v>
+        <v>2.54011940956116</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>2.62737560272217</v>
+        <v>2.62737584114075</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G61" t="n">
-        <v>2.53042459487915</v>
+        <v>2.53042435646057</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>2.81158304214478</v>
+        <v>2.8115828037262</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.88914394378662</v>
+        <v>2.88914370536804</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.03457045555115</v>
+        <v>3.03457069396973</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G89" t="n">
-        <v>3.09274125099182</v>
+        <v>3.09274101257324</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.21877765655518</v>
+        <v>3.2187774181366</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3545093536377</v>
+        <v>3.35450911521912</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>3.53871631622314</v>
+        <v>3.53871655464172</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.17030191421509</v>
+        <v>3.17030215263367</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G109" t="n">
-        <v>3.21877765655518</v>
+        <v>3.2187774181366</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>3.3545093536377</v>
+        <v>3.35450911521912</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>3.03457045555115</v>
+        <v>3.03457069396973</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G125" t="n">
-        <v>2.97639966011047</v>
+        <v>2.97639989852905</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>3.12182641029358</v>
+        <v>3.12182664871216</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>3.38359451293945</v>
+        <v>3.38359475135803</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.5</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39328956604004</v>
+        <v>3.39328980445862</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G141" t="n">
-        <v>3.20908260345459</v>
+        <v>3.20908236503601</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G144" t="n">
-        <v>3.49993586540222</v>
+        <v>3.49993562698364</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>3.77139925956726</v>
+        <v>3.77139902114868</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>3.53871631622314</v>
+        <v>3.53871655464172</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G167" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G169" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G179" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G184" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G191" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G192" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G195" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G216" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>3.9653012752533</v>
+        <v>3.96530151367188</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14950895309448</v>
+        <v>4.14950847625732</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G234" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G237" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G248" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>4.10103321075439</v>
+        <v>4.10103273391724</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G256" t="n">
-        <v>3.9653012752533</v>
+        <v>3.96530151367188</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>4.41127681732178</v>
+        <v>4.41127634048462</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G276" t="n">
-        <v>4.14950895309448</v>
+        <v>4.14950847625732</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>4.10103321075439</v>
+        <v>4.10103273391724</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.75200891494751</v>
+        <v>3.75200867652893</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.57749676704407</v>
+        <v>3.57749700546265</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G291" t="n">
-        <v>3.58719182014465</v>
+        <v>3.58719205856323</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G295" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.75</v>
       </c>
       <c r="G296" t="n">
-        <v>3.63566756248474</v>
+        <v>3.63566732406616</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G304" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G308" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.25</v>
       </c>
       <c r="G319" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.25</v>
       </c>
       <c r="G321" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.25</v>
       </c>
       <c r="G325" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>4.32402038574219</v>
+        <v>4.32402086257935</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G338" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>4.45005702972412</v>
+        <v>4.45005750656128</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>4.6148738861084</v>
+        <v>4.61487436294556</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G359" t="n">
-        <v>5.0608491897583</v>
+        <v>5.06084871292114</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>4.63426399230957</v>
+        <v>4.63426446914673</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>4.6148738861084</v>
+        <v>4.61487436294556</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>4.45005702972412</v>
+        <v>4.45005750656128</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G367" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>5.0996298789978</v>
+        <v>5.09962940216064</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>4.79908132553101</v>
+        <v>4.79908084869385</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.80048441886902</v>
+        <v>3.8004846572876</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>3.94591116905212</v>
+        <v>3.9459114074707</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G414" t="n">
-        <v>3.62597250938416</v>
+        <v>3.62597227096558</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.49993586540222</v>
+        <v>3.49993562698364</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G426" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.63566756248474</v>
+        <v>3.63566732406616</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G432" t="n">
-        <v>3.77139925956726</v>
+        <v>3.77139902114868</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90713095664978</v>
+        <v>3.9071307182312</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G436" t="n">
-        <v>3.84895992279053</v>
+        <v>3.84896016120911</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.94591116905212</v>
+        <v>3.9459114074707</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G439" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -20080,6 +20080,32 @@
         <v>4.09999990463257</v>
       </c>
       <c r="H758" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B759" t="n">
+        <v>5010</v>
+      </c>
+      <c r="C759" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="D759" t="n">
+        <v>4.03999996185303</v>
+      </c>
+      <c r="E759" t="n">
+        <v>4.03999996185303</v>
+      </c>
+      <c r="F759" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="G759" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="H759" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G3" t="n">
-        <v>2.40923547744751</v>
+        <v>2.40923571586609</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46740627288818</v>
+        <v>2.46740651130676</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.47710132598877</v>
+        <v>2.47710156440735</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54011940956116</v>
+        <v>2.54011964797974</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4577112197876</v>
+        <v>2.45771145820618</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>2.40438795089722</v>
+        <v>2.4043881893158</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.37530279159546</v>
+        <v>2.37530303001404</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>2.30743718147278</v>
+        <v>2.3074369430542</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.37530279159546</v>
+        <v>2.37530303001404</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>2.56920528411865</v>
+        <v>2.56920504570007</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.54981470108032</v>
+        <v>2.5498149394989</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>2.54011940956116</v>
+        <v>2.54011964797974</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>2.62737584114075</v>
+        <v>2.62737560272217</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G61" t="n">
-        <v>2.53042435646057</v>
+        <v>2.53042459487915</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8115828037262</v>
+        <v>2.81158304214478</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.88914370536804</v>
+        <v>2.88914394378662</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.03457069396973</v>
+        <v>3.03457045555115</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G89" t="n">
-        <v>3.09274101257324</v>
+        <v>3.09274125099182</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.2187774181366</v>
+        <v>3.21877765655518</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.35450911521912</v>
+        <v>3.3545093536377</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>3.53871655464172</v>
+        <v>3.53871631622314</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.17030215263367</v>
+        <v>3.17030191421509</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G109" t="n">
-        <v>3.2187774181366</v>
+        <v>3.21877765655518</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>3.35450911521912</v>
+        <v>3.3545093536377</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>3.03457069396973</v>
+        <v>3.03457045555115</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G125" t="n">
-        <v>2.97639989852905</v>
+        <v>2.97639966011047</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>3.12182664871216</v>
+        <v>3.12182641029358</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>3.38359475135803</v>
+        <v>3.38359451293945</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.5</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39328980445862</v>
+        <v>3.39328956604004</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G141" t="n">
-        <v>3.20908236503601</v>
+        <v>3.20908260345459</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G144" t="n">
-        <v>3.49993562698364</v>
+        <v>3.49993586540222</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>3.77139902114868</v>
+        <v>3.77139925956726</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>3.53871655464172</v>
+        <v>3.53871631622314</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G167" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G169" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G179" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G184" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G191" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G192" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G195" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G216" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>3.96530151367188</v>
+        <v>3.9653012752533</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14950847625732</v>
+        <v>4.14950895309448</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G234" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G237" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G248" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>4.10103273391724</v>
+        <v>4.10103321075439</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G256" t="n">
-        <v>3.96530151367188</v>
+        <v>3.9653012752533</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>4.41127634048462</v>
+        <v>4.41127681732178</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G276" t="n">
-        <v>4.14950847625732</v>
+        <v>4.14950895309448</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>4.10103273391724</v>
+        <v>4.10103321075439</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.75200867652893</v>
+        <v>3.75200891494751</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.57749700546265</v>
+        <v>3.57749676704407</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G291" t="n">
-        <v>3.58719205856323</v>
+        <v>3.58719182014465</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G295" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.75</v>
       </c>
       <c r="G296" t="n">
-        <v>3.63566732406616</v>
+        <v>3.63566756248474</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G304" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G308" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.25</v>
       </c>
       <c r="G319" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.25</v>
       </c>
       <c r="G321" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.25</v>
       </c>
       <c r="G325" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>4.32402086257935</v>
+        <v>4.32402038574219</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G338" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>4.45005750656128</v>
+        <v>4.45005702972412</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>4.61487436294556</v>
+        <v>4.6148738861084</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G359" t="n">
-        <v>5.06084871292114</v>
+        <v>5.0608491897583</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>4.63426446914673</v>
+        <v>4.63426399230957</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>4.61487436294556</v>
+        <v>4.6148738861084</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>4.45005750656128</v>
+        <v>4.45005702972412</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G367" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>5.09962940216064</v>
+        <v>5.0996298789978</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>4.79908084869385</v>
+        <v>4.79908132553101</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.8004846572876</v>
+        <v>3.80048441886902</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>3.9459114074707</v>
+        <v>3.94591116905212</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G414" t="n">
-        <v>3.62597227096558</v>
+        <v>3.62597250938416</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.49993562698364</v>
+        <v>3.49993586540222</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G426" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.63566732406616</v>
+        <v>3.63566756248474</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G432" t="n">
-        <v>3.77139902114868</v>
+        <v>3.77139925956726</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>3.9071307182312</v>
+        <v>3.90713095664978</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G436" t="n">
-        <v>3.84896016120911</v>
+        <v>3.84895992279053</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.9459114074707</v>
+        <v>3.94591116905212</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G439" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -20106,6 +20106,32 @@
         <v>4.19999980926514</v>
       </c>
       <c r="H759" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B760" t="n">
+        <v>6724</v>
+      </c>
+      <c r="C760" t="n">
+        <v>4.17999982833862</v>
+      </c>
+      <c r="D760" t="n">
+        <v>4.03000020980835</v>
+      </c>
+      <c r="E760" t="n">
+        <v>4.17999982833862</v>
+      </c>
+      <c r="F760" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="G760" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="H760" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G3" t="n">
-        <v>2.40923571586609</v>
+        <v>2.40923547744751</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46740651130676</v>
+        <v>2.46740627288818</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.47710156440735</v>
+        <v>2.47710132598877</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54011964797974</v>
+        <v>2.54011940956116</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>2.45771145820618</v>
+        <v>2.4577112197876</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>2.4043881893158</v>
+        <v>2.40438795089722</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.37530303001404</v>
+        <v>2.37530279159546</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>2.3074369430542</v>
+        <v>2.30743718147278</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.37530303001404</v>
+        <v>2.37530279159546</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>2.56920504570007</v>
+        <v>2.56920528411865</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.5498149394989</v>
+        <v>2.54981470108032</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>2.54011964797974</v>
+        <v>2.54011940956116</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>2.62737560272217</v>
+        <v>2.62737584114075</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G61" t="n">
-        <v>2.53042459487915</v>
+        <v>2.53042435646057</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>2.81158304214478</v>
+        <v>2.8115828037262</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.88914394378662</v>
+        <v>2.88914370536804</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.03457045555115</v>
+        <v>3.03457069396973</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G89" t="n">
-        <v>3.09274125099182</v>
+        <v>3.09274101257324</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.21877765655518</v>
+        <v>3.2187774181366</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3545093536377</v>
+        <v>3.35450911521912</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>3.53871631622314</v>
+        <v>3.53871655464172</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.17030191421509</v>
+        <v>3.17030215263367</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G109" t="n">
-        <v>3.21877765655518</v>
+        <v>3.2187774181366</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>3.3545093536377</v>
+        <v>3.35450911521912</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>3.03457045555115</v>
+        <v>3.03457069396973</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G125" t="n">
-        <v>2.97639966011047</v>
+        <v>2.97639989852905</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>3.12182641029358</v>
+        <v>3.12182664871216</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>3.38359451293945</v>
+        <v>3.38359475135803</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.5</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39328956604004</v>
+        <v>3.39328980445862</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G141" t="n">
-        <v>3.20908260345459</v>
+        <v>3.20908236503601</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G144" t="n">
-        <v>3.49993586540222</v>
+        <v>3.49993562698364</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>3.77139925956726</v>
+        <v>3.77139902114868</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>3.53871631622314</v>
+        <v>3.53871655464172</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G167" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G169" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G179" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G184" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G191" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G192" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G195" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G216" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>3.9653012752533</v>
+        <v>3.96530151367188</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14950895309448</v>
+        <v>4.14950847625732</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G234" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G237" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G248" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>4.10103321075439</v>
+        <v>4.10103273391724</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G256" t="n">
-        <v>3.9653012752533</v>
+        <v>3.96530151367188</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>4.41127681732178</v>
+        <v>4.41127634048462</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G276" t="n">
-        <v>4.14950895309448</v>
+        <v>4.14950847625732</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>4.10103321075439</v>
+        <v>4.10103273391724</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.75200891494751</v>
+        <v>3.75200867652893</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.57749676704407</v>
+        <v>3.57749700546265</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G291" t="n">
-        <v>3.58719182014465</v>
+        <v>3.58719205856323</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G295" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.75</v>
       </c>
       <c r="G296" t="n">
-        <v>3.63566756248474</v>
+        <v>3.63566732406616</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G304" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G308" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.25</v>
       </c>
       <c r="G319" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.25</v>
       </c>
       <c r="G321" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.25</v>
       </c>
       <c r="G325" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>4.32402038574219</v>
+        <v>4.32402086257935</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G338" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>4.45005702972412</v>
+        <v>4.45005750656128</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>4.6148738861084</v>
+        <v>4.61487436294556</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G359" t="n">
-        <v>5.0608491897583</v>
+        <v>5.06084871292114</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>4.63426399230957</v>
+        <v>4.63426446914673</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>4.6148738861084</v>
+        <v>4.61487436294556</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>4.45005702972412</v>
+        <v>4.45005750656128</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G367" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>5.0996298789978</v>
+        <v>5.09962940216064</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>4.79908132553101</v>
+        <v>4.79908084869385</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.80048441886902</v>
+        <v>3.8004846572876</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>3.94591116905212</v>
+        <v>3.9459114074707</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G414" t="n">
-        <v>3.62597250938416</v>
+        <v>3.62597227096558</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.49993586540222</v>
+        <v>3.49993562698364</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G426" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.63566756248474</v>
+        <v>3.63566732406616</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G432" t="n">
-        <v>3.77139925956726</v>
+        <v>3.77139902114868</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90713095664978</v>
+        <v>3.9071307182312</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G436" t="n">
-        <v>3.84895992279053</v>
+        <v>3.84896016120911</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.94591116905212</v>
+        <v>3.9459114074707</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G439" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -20184,6 +20184,32 @@
         <v>3.84999990463257</v>
       </c>
       <c r="H762" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B763" t="n">
+        <v>23908</v>
+      </c>
+      <c r="C763" t="n">
+        <v>4.07000017166138</v>
+      </c>
+      <c r="D763" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="E763" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="F763" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="G763" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="H763" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -17983,8 +17983,31 @@
       <c r="E766" t="n">
         <v>3.85999989509583</v>
       </c>
-      <c r="F766"/>
+      <c r="F766" t="n">
+        <v>3.75</v>
+      </c>
       <c r="G766" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B767" t="n">
+        <v>8626</v>
+      </c>
+      <c r="C767" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="D767" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E767" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="F767"/>
+      <c r="G767" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -18006,8 +18006,31 @@
       <c r="E767" t="n">
         <v>3.75999999046326</v>
       </c>
-      <c r="F767"/>
+      <c r="F767" t="n">
+        <v>3.79999995231628</v>
+      </c>
       <c r="G767" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B768" t="n">
+        <v>3315</v>
+      </c>
+      <c r="C768" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D768" t="n">
+        <v>3.82999992370605</v>
+      </c>
+      <c r="E768" t="n">
+        <v>3.82999992370605</v>
+      </c>
+      <c r="F768"/>
+      <c r="G768" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -18021,7 +18021,7 @@
         <v>3315</v>
       </c>
       <c r="C768" t="n">
-        <v>3.90000009536743</v>
+        <v>3.91000008583069</v>
       </c>
       <c r="D768" t="n">
         <v>3.82999992370605</v>
@@ -18029,8 +18029,31 @@
       <c r="E768" t="n">
         <v>3.82999992370605</v>
       </c>
-      <c r="F768"/>
+      <c r="F768" t="n">
+        <v>3.91000008583069</v>
+      </c>
       <c r="G768" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B769" t="n">
+        <v>9321</v>
+      </c>
+      <c r="C769" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="D769" t="n">
+        <v>3.89000010490417</v>
+      </c>
+      <c r="E769" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="F769"/>
+      <c r="G769" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -18052,8 +18052,31 @@
       <c r="E769" t="n">
         <v>3.9300000667572</v>
       </c>
-      <c r="F769"/>
+      <c r="F769" t="n">
+        <v>3.91000008583069</v>
+      </c>
       <c r="G769" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B770" t="n">
+        <v>3557</v>
+      </c>
+      <c r="C770" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="D770" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="E770" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="F770"/>
+      <c r="G770" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -18082,6 +18082,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="771">
+      <c r="A771" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B771" t="n">
+        <v>1979</v>
+      </c>
+      <c r="C771" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D771" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="E771" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="F771" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="G771" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -20473,6 +20473,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B774" t="n">
+        <v>120</v>
+      </c>
+      <c r="C774" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="D774" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="E774" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="F774" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="G774" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="H774" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G3" t="n">
-        <v>2.40923571586609</v>
+        <v>2.40923547744751</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46740651130676</v>
+        <v>2.46740627288818</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.47710156440735</v>
+        <v>2.47710132598877</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54011964797974</v>
+        <v>2.54011940956116</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>2.45771145820618</v>
+        <v>2.4577112197876</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>2.4043881893158</v>
+        <v>2.40438795089722</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.37530303001404</v>
+        <v>2.37530279159546</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>2.3074369430542</v>
+        <v>2.30743718147278</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.37530303001404</v>
+        <v>2.37530279159546</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>2.56920504570007</v>
+        <v>2.56920528411865</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.5498149394989</v>
+        <v>2.54981470108032</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>2.54011964797974</v>
+        <v>2.54011940956116</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>2.62737560272217</v>
+        <v>2.62737584114075</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G61" t="n">
-        <v>2.53042459487915</v>
+        <v>2.53042435646057</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>2.81158304214478</v>
+        <v>2.8115828037262</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.88914394378662</v>
+        <v>2.88914370536804</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.03457045555115</v>
+        <v>3.03457069396973</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G89" t="n">
-        <v>3.09274125099182</v>
+        <v>3.09274101257324</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.21877765655518</v>
+        <v>3.2187774181366</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3545093536377</v>
+        <v>3.35450911521912</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>3.53871631622314</v>
+        <v>3.53871655464172</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.17030191421509</v>
+        <v>3.17030215263367</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G109" t="n">
-        <v>3.21877765655518</v>
+        <v>3.2187774181366</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>3.3545093536377</v>
+        <v>3.35450911521912</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>3.03457045555115</v>
+        <v>3.03457069396973</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G125" t="n">
-        <v>2.97639966011047</v>
+        <v>2.97639989852905</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>3.12182641029358</v>
+        <v>3.12182664871216</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>3.38359451293945</v>
+        <v>3.38359475135803</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.5</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39328956604004</v>
+        <v>3.39328980445862</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G141" t="n">
-        <v>3.20908260345459</v>
+        <v>3.20908236503601</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G144" t="n">
-        <v>3.49993586540222</v>
+        <v>3.49993562698364</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>3.77139925956726</v>
+        <v>3.77139902114868</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>3.53871631622314</v>
+        <v>3.53871655464172</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G167" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G169" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G179" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G184" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G191" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G192" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G195" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G216" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>3.9653012752533</v>
+        <v>3.96530151367188</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14950895309448</v>
+        <v>4.14950847625732</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G234" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G237" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G248" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>4.10103321075439</v>
+        <v>4.10103273391724</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G256" t="n">
-        <v>3.9653012752533</v>
+        <v>3.96530151367188</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>4.41127681732178</v>
+        <v>4.41127634048462</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G276" t="n">
-        <v>4.14950895309448</v>
+        <v>4.14950847625732</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>4.10103321075439</v>
+        <v>4.10103273391724</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.75200891494751</v>
+        <v>3.75200867652893</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.57749676704407</v>
+        <v>3.57749700546265</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G291" t="n">
-        <v>3.58719182014465</v>
+        <v>3.58719205856323</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G295" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.75</v>
       </c>
       <c r="G296" t="n">
-        <v>3.63566756248474</v>
+        <v>3.63566732406616</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G304" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G308" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.25</v>
       </c>
       <c r="G319" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.25</v>
       </c>
       <c r="G321" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.25</v>
       </c>
       <c r="G325" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>4.32402038574219</v>
+        <v>4.32402086257935</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G338" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>4.45005702972412</v>
+        <v>4.45005750656128</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>4.6148738861084</v>
+        <v>4.61487436294556</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G359" t="n">
-        <v>5.0608491897583</v>
+        <v>5.06084871292114</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>4.63426399230957</v>
+        <v>4.63426446914673</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>4.6148738861084</v>
+        <v>4.61487436294556</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>4.45005702972412</v>
+        <v>4.45005750656128</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G367" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>5.0996298789978</v>
+        <v>5.09962940216064</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>4.79908132553101</v>
+        <v>4.79908084869385</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.80048441886902</v>
+        <v>3.8004846572876</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>3.94591116905212</v>
+        <v>3.9459114074707</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G414" t="n">
-        <v>3.62597250938416</v>
+        <v>3.62597227096558</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.49993586540222</v>
+        <v>3.49993562698364</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G426" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.63566756248474</v>
+        <v>3.63566732406616</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G432" t="n">
-        <v>3.77139925956726</v>
+        <v>3.77139902114868</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90713095664978</v>
+        <v>3.9071307182312</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G436" t="n">
-        <v>3.84895992279053</v>
+        <v>3.84896016120911</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.94591116905212</v>
+        <v>3.9459114074707</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G439" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -20496,6 +20496,32 @@
         <v>3.96000003814697</v>
       </c>
       <c r="H774" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B775" t="n">
+        <v>4743</v>
+      </c>
+      <c r="C775" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="D775" t="n">
+        <v>3.89000010490417</v>
+      </c>
+      <c r="E775" t="n">
+        <v>3.89000010490417</v>
+      </c>
+      <c r="F775" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G775" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="H775" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G3" t="n">
-        <v>2.40923571586609</v>
+        <v>2.40923547744751</v>
       </c>
       <c r="H3" t="n">
         <v>24435</v>
@@ -949,7 +949,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46740651130676</v>
+        <v>2.46740627288818</v>
       </c>
       <c r="H20" t="n">
         <v>120</v>
@@ -1036,7 +1036,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.47710156440735</v>
+        <v>2.47710132598877</v>
       </c>
       <c r="H23" t="n">
         <v>500</v>
@@ -1152,7 +1152,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54011964797974</v>
+        <v>2.54011940956116</v>
       </c>
       <c r="H27" t="n">
         <v>3600</v>
@@ -1326,7 +1326,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>2.45771145820618</v>
+        <v>2.4577112197876</v>
       </c>
       <c r="H33" t="n">
         <v>643</v>
@@ -1384,7 +1384,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H35" t="n">
         <v>16336</v>
@@ -1471,7 +1471,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>2.4043881893158</v>
+        <v>2.40438795089722</v>
       </c>
       <c r="H38" t="n">
         <v>2500</v>
@@ -1500,7 +1500,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.37530303001404</v>
+        <v>2.37530279159546</v>
       </c>
       <c r="H39" t="n">
         <v>10844</v>
@@ -1529,7 +1529,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>2.3074369430542</v>
+        <v>2.30743718147278</v>
       </c>
       <c r="H40" t="n">
         <v>9875</v>
@@ -1558,7 +1558,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.37530303001404</v>
+        <v>2.37530279159546</v>
       </c>
       <c r="H41" t="n">
         <v>5467</v>
@@ -1790,7 +1790,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H49" t="n">
         <v>1601</v>
@@ -1877,7 +1877,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H52" t="n">
         <v>3895</v>
@@ -1935,7 +1935,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>2.56920504570007</v>
+        <v>2.56920528411865</v>
       </c>
       <c r="H54" t="n">
         <v>626</v>
@@ -1964,7 +1964,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.5498149394989</v>
+        <v>2.54981470108032</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -2051,7 +2051,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>2.54011964797974</v>
+        <v>2.54011940956116</v>
       </c>
       <c r="H58" t="n">
         <v>9659</v>
@@ -2109,7 +2109,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>2.62737560272217</v>
+        <v>2.62737584114075</v>
       </c>
       <c r="H60" t="n">
         <v>1381</v>
@@ -2138,7 +2138,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G61" t="n">
-        <v>2.53042459487915</v>
+        <v>2.53042435646057</v>
       </c>
       <c r="H61" t="n">
         <v>14026</v>
@@ -2515,7 +2515,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>2.81158304214478</v>
+        <v>2.8115828037262</v>
       </c>
       <c r="H74" t="n">
         <v>20161</v>
@@ -2544,7 +2544,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H75" t="n">
         <v>41308</v>
@@ -2573,7 +2573,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.88914394378662</v>
+        <v>2.88914370536804</v>
       </c>
       <c r="H76" t="n">
         <v>7786</v>
@@ -2602,7 +2602,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H77" t="n">
         <v>1600</v>
@@ -2805,7 +2805,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H84" t="n">
         <v>7079</v>
@@ -2921,7 +2921,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.03457045555115</v>
+        <v>3.03457069396973</v>
       </c>
       <c r="H88" t="n">
         <v>37120</v>
@@ -2950,7 +2950,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G89" t="n">
-        <v>3.09274125099182</v>
+        <v>3.09274101257324</v>
       </c>
       <c r="H89" t="n">
         <v>2382</v>
@@ -2979,7 +2979,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.21877765655518</v>
+        <v>3.2187774181366</v>
       </c>
       <c r="H90" t="n">
         <v>14770</v>
@@ -3008,7 +3008,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3545093536377</v>
+        <v>3.35450911521912</v>
       </c>
       <c r="H91" t="n">
         <v>19914</v>
@@ -3124,7 +3124,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>3.53871631622314</v>
+        <v>3.53871655464172</v>
       </c>
       <c r="H95" t="n">
         <v>10830</v>
@@ -3269,7 +3269,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H100" t="n">
         <v>6418</v>
@@ -3298,7 +3298,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H101" t="n">
         <v>8677</v>
@@ -3327,7 +3327,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H102" t="n">
         <v>2458</v>
@@ -3356,7 +3356,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H103" t="n">
         <v>3214</v>
@@ -3443,7 +3443,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.17030191421509</v>
+        <v>3.17030215263367</v>
       </c>
       <c r="H106" t="n">
         <v>9695</v>
@@ -3530,7 +3530,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G109" t="n">
-        <v>3.21877765655518</v>
+        <v>3.2187774181366</v>
       </c>
       <c r="H109" t="n">
         <v>9752</v>
@@ -3646,7 +3646,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>3.3545093536377</v>
+        <v>3.35450911521912</v>
       </c>
       <c r="H113" t="n">
         <v>1800</v>
@@ -3849,7 +3849,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>3.03457045555115</v>
+        <v>3.03457069396973</v>
       </c>
       <c r="H120" t="n">
         <v>1575</v>
@@ -3994,7 +3994,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G125" t="n">
-        <v>2.97639966011047</v>
+        <v>2.97639989852905</v>
       </c>
       <c r="H125" t="n">
         <v>1040</v>
@@ -4197,7 +4197,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H132" t="n">
         <v>13414</v>
@@ -4226,7 +4226,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H133" t="n">
         <v>3706</v>
@@ -4255,7 +4255,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>3.12182641029358</v>
+        <v>3.12182664871216</v>
       </c>
       <c r="H134" t="n">
         <v>16322</v>
@@ -4371,7 +4371,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>3.38359451293945</v>
+        <v>3.38359475135803</v>
       </c>
       <c r="H138" t="n">
         <v>940</v>
@@ -4400,7 +4400,7 @@
         <v>3.5</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39328956604004</v>
+        <v>3.39328980445862</v>
       </c>
       <c r="H139" t="n">
         <v>2713</v>
@@ -4429,7 +4429,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H140" t="n">
         <v>25810</v>
@@ -4458,7 +4458,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G141" t="n">
-        <v>3.20908260345459</v>
+        <v>3.20908236503601</v>
       </c>
       <c r="H141" t="n">
         <v>9273</v>
@@ -4545,7 +4545,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G144" t="n">
-        <v>3.49993586540222</v>
+        <v>3.49993562698364</v>
       </c>
       <c r="H144" t="n">
         <v>7336</v>
@@ -4603,7 +4603,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>3.77139925956726</v>
+        <v>3.77139902114868</v>
       </c>
       <c r="H146" t="n">
         <v>19888</v>
@@ -5038,7 +5038,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>3.53871631622314</v>
+        <v>3.53871655464172</v>
       </c>
       <c r="H161" t="n">
         <v>11143</v>
@@ -5212,7 +5212,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G167" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H167" t="n">
         <v>19000</v>
@@ -5241,7 +5241,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H168" t="n">
         <v>8306</v>
@@ -5270,7 +5270,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G169" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H169" t="n">
         <v>4558</v>
@@ -5299,7 +5299,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H170" t="n">
         <v>2890</v>
@@ -5357,7 +5357,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H172" t="n">
         <v>3021</v>
@@ -5386,7 +5386,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H173" t="n">
         <v>502</v>
@@ -5531,7 +5531,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H178" t="n">
         <v>193</v>
@@ -5560,7 +5560,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G179" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H179" t="n">
         <v>200</v>
@@ -5705,7 +5705,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G184" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H184" t="n">
         <v>2570</v>
@@ -5821,7 +5821,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H188" t="n">
         <v>1553</v>
@@ -5850,7 +5850,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H189" t="n">
         <v>253</v>
@@ -5908,7 +5908,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G191" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H191" t="n">
         <v>550</v>
@@ -5937,7 +5937,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G192" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H194" t="n">
         <v>41</v>
@@ -6024,7 +6024,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G195" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H211" t="n">
         <v>2362</v>
@@ -6517,7 +6517,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H212" t="n">
         <v>2144</v>
@@ -6633,7 +6633,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G216" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H216" t="n">
         <v>1433</v>
@@ -6662,7 +6662,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>3.9653012752533</v>
+        <v>3.96530151367188</v>
       </c>
       <c r="H217" t="n">
         <v>152</v>
@@ -6691,7 +6691,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H218" t="n">
         <v>3009</v>
@@ -6865,7 +6865,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H224" t="n">
         <v>1205</v>
@@ -6952,7 +6952,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H227" t="n">
         <v>3822</v>
@@ -6981,7 +6981,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14950895309448</v>
+        <v>4.14950847625732</v>
       </c>
       <c r="H228" t="n">
         <v>2020</v>
@@ -7010,7 +7010,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H229" t="n">
         <v>305</v>
@@ -7155,7 +7155,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G234" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H234" t="n">
         <v>2110</v>
@@ -7213,7 +7213,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H236" t="n">
         <v>90</v>
@@ -7242,7 +7242,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G237" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G248" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H248" t="n">
         <v>4805</v>
@@ -7619,7 +7619,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H250" t="n">
         <v>2563</v>
@@ -7648,7 +7648,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>4.10103321075439</v>
+        <v>4.10103273391724</v>
       </c>
       <c r="H251" t="n">
         <v>185</v>
@@ -7764,7 +7764,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H255" t="n">
         <v>2204</v>
@@ -7793,7 +7793,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G256" t="n">
-        <v>3.9653012752533</v>
+        <v>3.96530151367188</v>
       </c>
       <c r="H256" t="n">
         <v>195</v>
@@ -8083,7 +8083,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H266" t="n">
         <v>1603</v>
@@ -8315,7 +8315,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>4.41127681732178</v>
+        <v>4.41127634048462</v>
       </c>
       <c r="H274" t="n">
         <v>5038</v>
@@ -8373,7 +8373,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G276" t="n">
-        <v>4.14950895309448</v>
+        <v>4.14950847625732</v>
       </c>
       <c r="H276" t="n">
         <v>710</v>
@@ -8547,7 +8547,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>4.10103321075439</v>
+        <v>4.10103273391724</v>
       </c>
       <c r="H282" t="n">
         <v>22</v>
@@ -8663,7 +8663,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.75200891494751</v>
+        <v>3.75200867652893</v>
       </c>
       <c r="H286" t="n">
         <v>6650</v>
@@ -8721,7 +8721,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.57749676704407</v>
+        <v>3.57749700546265</v>
       </c>
       <c r="H288" t="n">
         <v>5343</v>
@@ -8808,7 +8808,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G291" t="n">
-        <v>3.58719182014465</v>
+        <v>3.58719205856323</v>
       </c>
       <c r="H291" t="n">
         <v>186</v>
@@ -8924,7 +8924,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G295" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H295" t="n">
         <v>44240</v>
@@ -8953,7 +8953,7 @@
         <v>3.75</v>
       </c>
       <c r="G296" t="n">
-        <v>3.63566756248474</v>
+        <v>3.63566732406616</v>
       </c>
       <c r="H296" t="n">
         <v>6774</v>
@@ -9156,7 +9156,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H303" t="n">
         <v>10</v>
@@ -9185,7 +9185,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G304" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H304" t="n">
         <v>400</v>
@@ -9243,7 +9243,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H306" t="n">
         <v>100</v>
@@ -9272,7 +9272,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H307" t="n">
         <v>351</v>
@@ -9301,7 +9301,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G308" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>4.25</v>
       </c>
       <c r="G319" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H319" t="n">
         <v>2346</v>
@@ -9678,7 +9678,7 @@
         <v>4.25</v>
       </c>
       <c r="G321" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H321" t="n">
         <v>400</v>
@@ -9736,7 +9736,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H323" t="n">
         <v>6156</v>
@@ -9765,7 +9765,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H324" t="n">
         <v>50</v>
@@ -9794,7 +9794,7 @@
         <v>4.25</v>
       </c>
       <c r="G325" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H325" t="n">
         <v>2225</v>
@@ -9852,7 +9852,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H327" t="n">
         <v>1291</v>
@@ -9997,7 +9997,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H332" t="n">
         <v>2176</v>
@@ -10026,7 +10026,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>4.32402038574219</v>
+        <v>4.32402086257935</v>
       </c>
       <c r="H333" t="n">
         <v>6947</v>
@@ -10055,7 +10055,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H334" t="n">
         <v>2850</v>
@@ -10084,7 +10084,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H335" t="n">
         <v>3330</v>
@@ -10142,7 +10142,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H337" t="n">
         <v>1250</v>
@@ -10171,7 +10171,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G338" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>4.45005702972412</v>
+        <v>4.45005750656128</v>
       </c>
       <c r="H340" t="n">
         <v>3657</v>
@@ -10490,7 +10490,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H349" t="n">
         <v>275</v>
@@ -10519,7 +10519,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H350" t="n">
         <v>1768</v>
@@ -10664,7 +10664,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>4.6148738861084</v>
+        <v>4.61487436294556</v>
       </c>
       <c r="H355" t="n">
         <v>6262</v>
@@ -10693,7 +10693,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H356" t="n">
         <v>4002</v>
@@ -10780,7 +10780,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G359" t="n">
-        <v>5.0608491897583</v>
+        <v>5.06084871292114</v>
       </c>
       <c r="H359" t="n">
         <v>11409</v>
@@ -10838,7 +10838,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>4.63426399230957</v>
+        <v>4.63426446914673</v>
       </c>
       <c r="H361" t="n">
         <v>2991</v>
@@ -10867,7 +10867,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>4.6148738861084</v>
+        <v>4.61487436294556</v>
       </c>
       <c r="H362" t="n">
         <v>2537</v>
@@ -10896,7 +10896,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>4.45005702972412</v>
+        <v>4.45005750656128</v>
       </c>
       <c r="H363" t="n">
         <v>4303</v>
@@ -11012,7 +11012,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G367" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H367" t="n">
         <v>3131</v>
@@ -11041,7 +11041,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H368" t="n">
         <v>3753</v>
@@ -11215,7 +11215,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>5.0996298789978</v>
+        <v>5.09962940216064</v>
       </c>
       <c r="H374" t="n">
         <v>7576</v>
@@ -11331,7 +11331,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>4.79908132553101</v>
+        <v>4.79908084869385</v>
       </c>
       <c r="H378" t="n">
         <v>15636</v>
@@ -11447,7 +11447,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H382" t="n">
         <v>13041</v>
@@ -11795,7 +11795,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H394" t="n">
         <v>3776</v>
@@ -11911,7 +11911,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.80048441886902</v>
+        <v>3.8004846572876</v>
       </c>
       <c r="H398" t="n">
         <v>5798</v>
@@ -12056,7 +12056,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>3.94591116905212</v>
+        <v>3.9459114074707</v>
       </c>
       <c r="H403" t="n">
         <v>4450</v>
@@ -12375,7 +12375,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G414" t="n">
-        <v>3.62597250938416</v>
+        <v>3.62597227096558</v>
       </c>
       <c r="H414" t="n">
         <v>7546</v>
@@ -12694,7 +12694,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.49993586540222</v>
+        <v>3.49993562698364</v>
       </c>
       <c r="H425" t="n">
         <v>2789</v>
@@ -12723,7 +12723,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G426" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H426" t="n">
         <v>497</v>
@@ -12752,7 +12752,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H427" t="n">
         <v>10783</v>
@@ -12781,7 +12781,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H428" t="n">
         <v>103683</v>
@@ -12810,7 +12810,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.63566756248474</v>
+        <v>3.63566732406616</v>
       </c>
       <c r="H429" t="n">
         <v>10263</v>
@@ -12897,7 +12897,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G432" t="n">
-        <v>3.77139925956726</v>
+        <v>3.77139902114868</v>
       </c>
       <c r="H432" t="n">
         <v>18537</v>
@@ -12926,7 +12926,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90713095664978</v>
+        <v>3.9071307182312</v>
       </c>
       <c r="H433" t="n">
         <v>7020</v>
@@ -13013,7 +13013,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G436" t="n">
-        <v>3.84895992279053</v>
+        <v>3.84896016120911</v>
       </c>
       <c r="H436" t="n">
         <v>3204</v>
@@ -13071,7 +13071,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.94591116905212</v>
+        <v>3.9459114074707</v>
       </c>
       <c r="H438" t="n">
         <v>7716</v>
@@ -13100,7 +13100,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G439" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H439" t="n">
         <v>1963</v>
@@ -22879,6 +22879,35 @@
         <v>10</v>
       </c>
       <c r="I776" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="s">
+        <v>9</v>
+      </c>
+      <c r="B777" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C777" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D777" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="E777" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="F777" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="G777" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="H777" t="n">
+        <v>7743</v>
+      </c>
+      <c r="I777" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G3" t="n">
-        <v>2.40923547744751</v>
+        <v>2.40923571586609</v>
       </c>
       <c r="H3" t="n">
         <v>24435</v>
@@ -949,7 +949,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46740627288818</v>
+        <v>2.46740651130676</v>
       </c>
       <c r="H20" t="n">
         <v>120</v>
@@ -1036,7 +1036,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.47710132598877</v>
+        <v>2.47710156440735</v>
       </c>
       <c r="H23" t="n">
         <v>500</v>
@@ -1152,7 +1152,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54011940956116</v>
+        <v>2.54011964797974</v>
       </c>
       <c r="H27" t="n">
         <v>3600</v>
@@ -1326,7 +1326,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4577112197876</v>
+        <v>2.45771145820618</v>
       </c>
       <c r="H33" t="n">
         <v>643</v>
@@ -1384,7 +1384,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H35" t="n">
         <v>16336</v>
@@ -1471,7 +1471,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>2.40438795089722</v>
+        <v>2.4043881893158</v>
       </c>
       <c r="H38" t="n">
         <v>2500</v>
@@ -1500,7 +1500,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.37530279159546</v>
+        <v>2.37530303001404</v>
       </c>
       <c r="H39" t="n">
         <v>10844</v>
@@ -1529,7 +1529,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>2.30743718147278</v>
+        <v>2.3074369430542</v>
       </c>
       <c r="H40" t="n">
         <v>9875</v>
@@ -1558,7 +1558,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.37530279159546</v>
+        <v>2.37530303001404</v>
       </c>
       <c r="H41" t="n">
         <v>5467</v>
@@ -1790,7 +1790,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H49" t="n">
         <v>1601</v>
@@ -1877,7 +1877,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H52" t="n">
         <v>3895</v>
@@ -1935,7 +1935,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>2.56920528411865</v>
+        <v>2.56920504570007</v>
       </c>
       <c r="H54" t="n">
         <v>626</v>
@@ -1964,7 +1964,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.54981470108032</v>
+        <v>2.5498149394989</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -2051,7 +2051,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>2.54011940956116</v>
+        <v>2.54011964797974</v>
       </c>
       <c r="H58" t="n">
         <v>9659</v>
@@ -2109,7 +2109,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>2.62737584114075</v>
+        <v>2.62737560272217</v>
       </c>
       <c r="H60" t="n">
         <v>1381</v>
@@ -2138,7 +2138,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G61" t="n">
-        <v>2.53042435646057</v>
+        <v>2.53042459487915</v>
       </c>
       <c r="H61" t="n">
         <v>14026</v>
@@ -2515,7 +2515,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8115828037262</v>
+        <v>2.81158304214478</v>
       </c>
       <c r="H74" t="n">
         <v>20161</v>
@@ -2544,7 +2544,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H75" t="n">
         <v>41308</v>
@@ -2573,7 +2573,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.88914370536804</v>
+        <v>2.88914394378662</v>
       </c>
       <c r="H76" t="n">
         <v>7786</v>
@@ -2602,7 +2602,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H77" t="n">
         <v>1600</v>
@@ -2805,7 +2805,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H84" t="n">
         <v>7079</v>
@@ -2921,7 +2921,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.03457069396973</v>
+        <v>3.03457045555115</v>
       </c>
       <c r="H88" t="n">
         <v>37120</v>
@@ -2950,7 +2950,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G89" t="n">
-        <v>3.09274101257324</v>
+        <v>3.09274125099182</v>
       </c>
       <c r="H89" t="n">
         <v>2382</v>
@@ -2979,7 +2979,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.2187774181366</v>
+        <v>3.21877765655518</v>
       </c>
       <c r="H90" t="n">
         <v>14770</v>
@@ -3008,7 +3008,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.35450911521912</v>
+        <v>3.3545093536377</v>
       </c>
       <c r="H91" t="n">
         <v>19914</v>
@@ -3124,7 +3124,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>3.53871655464172</v>
+        <v>3.53871631622314</v>
       </c>
       <c r="H95" t="n">
         <v>10830</v>
@@ -3269,7 +3269,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H100" t="n">
         <v>6418</v>
@@ -3298,7 +3298,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H101" t="n">
         <v>8677</v>
@@ -3327,7 +3327,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H102" t="n">
         <v>2458</v>
@@ -3356,7 +3356,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H103" t="n">
         <v>3214</v>
@@ -3443,7 +3443,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.17030215263367</v>
+        <v>3.17030191421509</v>
       </c>
       <c r="H106" t="n">
         <v>9695</v>
@@ -3530,7 +3530,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G109" t="n">
-        <v>3.2187774181366</v>
+        <v>3.21877765655518</v>
       </c>
       <c r="H109" t="n">
         <v>9752</v>
@@ -3646,7 +3646,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>3.35450911521912</v>
+        <v>3.3545093536377</v>
       </c>
       <c r="H113" t="n">
         <v>1800</v>
@@ -3849,7 +3849,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>3.03457069396973</v>
+        <v>3.03457045555115</v>
       </c>
       <c r="H120" t="n">
         <v>1575</v>
@@ -3994,7 +3994,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G125" t="n">
-        <v>2.97639989852905</v>
+        <v>2.97639966011047</v>
       </c>
       <c r="H125" t="n">
         <v>1040</v>
@@ -4197,7 +4197,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H132" t="n">
         <v>13414</v>
@@ -4226,7 +4226,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H133" t="n">
         <v>3706</v>
@@ -4255,7 +4255,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>3.12182664871216</v>
+        <v>3.12182641029358</v>
       </c>
       <c r="H134" t="n">
         <v>16322</v>
@@ -4371,7 +4371,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>3.38359475135803</v>
+        <v>3.38359451293945</v>
       </c>
       <c r="H138" t="n">
         <v>940</v>
@@ -4400,7 +4400,7 @@
         <v>3.5</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39328980445862</v>
+        <v>3.39328956604004</v>
       </c>
       <c r="H139" t="n">
         <v>2713</v>
@@ -4429,7 +4429,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H140" t="n">
         <v>25810</v>
@@ -4458,7 +4458,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G141" t="n">
-        <v>3.20908236503601</v>
+        <v>3.20908260345459</v>
       </c>
       <c r="H141" t="n">
         <v>9273</v>
@@ -4545,7 +4545,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G144" t="n">
-        <v>3.49993562698364</v>
+        <v>3.49993586540222</v>
       </c>
       <c r="H144" t="n">
         <v>7336</v>
@@ -4603,7 +4603,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>3.77139902114868</v>
+        <v>3.77139925956726</v>
       </c>
       <c r="H146" t="n">
         <v>19888</v>
@@ -5038,7 +5038,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>3.53871655464172</v>
+        <v>3.53871631622314</v>
       </c>
       <c r="H161" t="n">
         <v>11143</v>
@@ -5212,7 +5212,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G167" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H167" t="n">
         <v>19000</v>
@@ -5241,7 +5241,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H168" t="n">
         <v>8306</v>
@@ -5270,7 +5270,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G169" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H169" t="n">
         <v>4558</v>
@@ -5299,7 +5299,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H170" t="n">
         <v>2890</v>
@@ -5357,7 +5357,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H172" t="n">
         <v>3021</v>
@@ -5386,7 +5386,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H173" t="n">
         <v>502</v>
@@ -5531,7 +5531,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H178" t="n">
         <v>193</v>
@@ -5560,7 +5560,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G179" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H179" t="n">
         <v>200</v>
@@ -5705,7 +5705,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G184" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H184" t="n">
         <v>2570</v>
@@ -5821,7 +5821,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H188" t="n">
         <v>1553</v>
@@ -5850,7 +5850,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H189" t="n">
         <v>253</v>
@@ -5908,7 +5908,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G191" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H191" t="n">
         <v>550</v>
@@ -5937,7 +5937,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G192" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H194" t="n">
         <v>41</v>
@@ -6024,7 +6024,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G195" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H211" t="n">
         <v>2362</v>
@@ -6517,7 +6517,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H212" t="n">
         <v>2144</v>
@@ -6633,7 +6633,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G216" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H216" t="n">
         <v>1433</v>
@@ -6662,7 +6662,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>3.96530151367188</v>
+        <v>3.9653012752533</v>
       </c>
       <c r="H217" t="n">
         <v>152</v>
@@ -6691,7 +6691,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H218" t="n">
         <v>3009</v>
@@ -6865,7 +6865,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H224" t="n">
         <v>1205</v>
@@ -6952,7 +6952,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H227" t="n">
         <v>3822</v>
@@ -6981,7 +6981,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14950847625732</v>
+        <v>4.14950895309448</v>
       </c>
       <c r="H228" t="n">
         <v>2020</v>
@@ -7010,7 +7010,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H229" t="n">
         <v>305</v>
@@ -7155,7 +7155,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G234" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H234" t="n">
         <v>2110</v>
@@ -7213,7 +7213,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H236" t="n">
         <v>90</v>
@@ -7242,7 +7242,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G237" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G248" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H248" t="n">
         <v>4805</v>
@@ -7619,7 +7619,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H250" t="n">
         <v>2563</v>
@@ -7648,7 +7648,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>4.10103273391724</v>
+        <v>4.10103321075439</v>
       </c>
       <c r="H251" t="n">
         <v>185</v>
@@ -7764,7 +7764,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H255" t="n">
         <v>2204</v>
@@ -7793,7 +7793,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G256" t="n">
-        <v>3.96530151367188</v>
+        <v>3.9653012752533</v>
       </c>
       <c r="H256" t="n">
         <v>195</v>
@@ -8083,7 +8083,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H266" t="n">
         <v>1603</v>
@@ -8315,7 +8315,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>4.41127634048462</v>
+        <v>4.41127681732178</v>
       </c>
       <c r="H274" t="n">
         <v>5038</v>
@@ -8373,7 +8373,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G276" t="n">
-        <v>4.14950847625732</v>
+        <v>4.14950895309448</v>
       </c>
       <c r="H276" t="n">
         <v>710</v>
@@ -8547,7 +8547,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>4.10103273391724</v>
+        <v>4.10103321075439</v>
       </c>
       <c r="H282" t="n">
         <v>22</v>
@@ -8663,7 +8663,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.75200867652893</v>
+        <v>3.75200891494751</v>
       </c>
       <c r="H286" t="n">
         <v>6650</v>
@@ -8721,7 +8721,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.57749700546265</v>
+        <v>3.57749676704407</v>
       </c>
       <c r="H288" t="n">
         <v>5343</v>
@@ -8808,7 +8808,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G291" t="n">
-        <v>3.58719205856323</v>
+        <v>3.58719182014465</v>
       </c>
       <c r="H291" t="n">
         <v>186</v>
@@ -8924,7 +8924,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G295" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H295" t="n">
         <v>44240</v>
@@ -8953,7 +8953,7 @@
         <v>3.75</v>
       </c>
       <c r="G296" t="n">
-        <v>3.63566732406616</v>
+        <v>3.63566756248474</v>
       </c>
       <c r="H296" t="n">
         <v>6774</v>
@@ -9156,7 +9156,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H303" t="n">
         <v>10</v>
@@ -9185,7 +9185,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G304" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H304" t="n">
         <v>400</v>
@@ -9243,7 +9243,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H306" t="n">
         <v>100</v>
@@ -9272,7 +9272,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H307" t="n">
         <v>351</v>
@@ -9301,7 +9301,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G308" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>4.25</v>
       </c>
       <c r="G319" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H319" t="n">
         <v>2346</v>
@@ -9678,7 +9678,7 @@
         <v>4.25</v>
       </c>
       <c r="G321" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H321" t="n">
         <v>400</v>
@@ -9736,7 +9736,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H323" t="n">
         <v>6156</v>
@@ -9765,7 +9765,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H324" t="n">
         <v>50</v>
@@ -9794,7 +9794,7 @@
         <v>4.25</v>
       </c>
       <c r="G325" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H325" t="n">
         <v>2225</v>
@@ -9852,7 +9852,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H327" t="n">
         <v>1291</v>
@@ -9997,7 +9997,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H332" t="n">
         <v>2176</v>
@@ -10026,7 +10026,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>4.32402086257935</v>
+        <v>4.32402038574219</v>
       </c>
       <c r="H333" t="n">
         <v>6947</v>
@@ -10055,7 +10055,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H334" t="n">
         <v>2850</v>
@@ -10084,7 +10084,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H335" t="n">
         <v>3330</v>
@@ -10142,7 +10142,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H337" t="n">
         <v>1250</v>
@@ -10171,7 +10171,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G338" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>4.45005750656128</v>
+        <v>4.45005702972412</v>
       </c>
       <c r="H340" t="n">
         <v>3657</v>
@@ -10490,7 +10490,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H349" t="n">
         <v>275</v>
@@ -10519,7 +10519,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H350" t="n">
         <v>1768</v>
@@ -10664,7 +10664,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>4.61487436294556</v>
+        <v>4.6148738861084</v>
       </c>
       <c r="H355" t="n">
         <v>6262</v>
@@ -10693,7 +10693,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H356" t="n">
         <v>4002</v>
@@ -10780,7 +10780,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G359" t="n">
-        <v>5.06084871292114</v>
+        <v>5.0608491897583</v>
       </c>
       <c r="H359" t="n">
         <v>11409</v>
@@ -10838,7 +10838,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>4.63426446914673</v>
+        <v>4.63426399230957</v>
       </c>
       <c r="H361" t="n">
         <v>2991</v>
@@ -10867,7 +10867,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>4.61487436294556</v>
+        <v>4.6148738861084</v>
       </c>
       <c r="H362" t="n">
         <v>2537</v>
@@ -10896,7 +10896,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>4.45005750656128</v>
+        <v>4.45005702972412</v>
       </c>
       <c r="H363" t="n">
         <v>4303</v>
@@ -11012,7 +11012,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G367" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H367" t="n">
         <v>3131</v>
@@ -11041,7 +11041,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H368" t="n">
         <v>3753</v>
@@ -11215,7 +11215,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>5.09962940216064</v>
+        <v>5.0996298789978</v>
       </c>
       <c r="H374" t="n">
         <v>7576</v>
@@ -11331,7 +11331,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>4.79908084869385</v>
+        <v>4.79908132553101</v>
       </c>
       <c r="H378" t="n">
         <v>15636</v>
@@ -11447,7 +11447,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H382" t="n">
         <v>13041</v>
@@ -11795,7 +11795,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H394" t="n">
         <v>3776</v>
@@ -11911,7 +11911,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.8004846572876</v>
+        <v>3.80048441886902</v>
       </c>
       <c r="H398" t="n">
         <v>5798</v>
@@ -12056,7 +12056,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>3.9459114074707</v>
+        <v>3.94591116905212</v>
       </c>
       <c r="H403" t="n">
         <v>4450</v>
@@ -12375,7 +12375,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G414" t="n">
-        <v>3.62597227096558</v>
+        <v>3.62597250938416</v>
       </c>
       <c r="H414" t="n">
         <v>7546</v>
@@ -12694,7 +12694,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.49993562698364</v>
+        <v>3.49993586540222</v>
       </c>
       <c r="H425" t="n">
         <v>2789</v>
@@ -12723,7 +12723,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G426" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H426" t="n">
         <v>497</v>
@@ -12752,7 +12752,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H427" t="n">
         <v>10783</v>
@@ -12781,7 +12781,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H428" t="n">
         <v>103683</v>
@@ -12810,7 +12810,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.63566732406616</v>
+        <v>3.63566756248474</v>
       </c>
       <c r="H429" t="n">
         <v>10263</v>
@@ -12897,7 +12897,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G432" t="n">
-        <v>3.77139902114868</v>
+        <v>3.77139925956726</v>
       </c>
       <c r="H432" t="n">
         <v>18537</v>
@@ -12926,7 +12926,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>3.9071307182312</v>
+        <v>3.90713095664978</v>
       </c>
       <c r="H433" t="n">
         <v>7020</v>
@@ -13013,7 +13013,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G436" t="n">
-        <v>3.84896016120911</v>
+        <v>3.84895992279053</v>
       </c>
       <c r="H436" t="n">
         <v>3204</v>
@@ -13071,7 +13071,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.9459114074707</v>
+        <v>3.94591116905212</v>
       </c>
       <c r="H438" t="n">
         <v>7716</v>
@@ -13100,7 +13100,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G439" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H439" t="n">
         <v>1963</v>
@@ -22908,6 +22908,35 @@
         <v>7743</v>
       </c>
       <c r="I777" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="s">
+        <v>9</v>
+      </c>
+      <c r="B778" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C778" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="D778" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="E778" t="n">
+        <v>3.84999990463257</v>
+      </c>
+      <c r="F778" t="n">
+        <v>3.89000010490417</v>
+      </c>
+      <c r="G778" t="n">
+        <v>3.89000010490417</v>
+      </c>
+      <c r="H778" t="n">
+        <v>6304</v>
+      </c>
+      <c r="I778" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G3" t="n">
-        <v>2.40923571586609</v>
+        <v>2.40923547744751</v>
       </c>
       <c r="H3" t="n">
         <v>24435</v>
@@ -949,7 +949,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46740651130676</v>
+        <v>2.46740627288818</v>
       </c>
       <c r="H20" t="n">
         <v>120</v>
@@ -1036,7 +1036,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.47710156440735</v>
+        <v>2.47710132598877</v>
       </c>
       <c r="H23" t="n">
         <v>500</v>
@@ -1152,7 +1152,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54011964797974</v>
+        <v>2.54011940956116</v>
       </c>
       <c r="H27" t="n">
         <v>3600</v>
@@ -1326,7 +1326,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>2.45771145820618</v>
+        <v>2.4577112197876</v>
       </c>
       <c r="H33" t="n">
         <v>643</v>
@@ -1384,7 +1384,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H35" t="n">
         <v>16336</v>
@@ -1471,7 +1471,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>2.4043881893158</v>
+        <v>2.40438795089722</v>
       </c>
       <c r="H38" t="n">
         <v>2500</v>
@@ -1500,7 +1500,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.37530303001404</v>
+        <v>2.37530279159546</v>
       </c>
       <c r="H39" t="n">
         <v>10844</v>
@@ -1529,7 +1529,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>2.3074369430542</v>
+        <v>2.30743718147278</v>
       </c>
       <c r="H40" t="n">
         <v>9875</v>
@@ -1558,7 +1558,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.37530303001404</v>
+        <v>2.37530279159546</v>
       </c>
       <c r="H41" t="n">
         <v>5467</v>
@@ -1790,7 +1790,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H49" t="n">
         <v>1601</v>
@@ -1877,7 +1877,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.48194909095764</v>
+        <v>2.48194885253906</v>
       </c>
       <c r="H52" t="n">
         <v>3895</v>
@@ -1935,7 +1935,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>2.56920504570007</v>
+        <v>2.56920528411865</v>
       </c>
       <c r="H54" t="n">
         <v>626</v>
@@ -1964,7 +1964,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.5498149394989</v>
+        <v>2.54981470108032</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -2051,7 +2051,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>2.54011964797974</v>
+        <v>2.54011940956116</v>
       </c>
       <c r="H58" t="n">
         <v>9659</v>
@@ -2109,7 +2109,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>2.62737560272217</v>
+        <v>2.62737584114075</v>
       </c>
       <c r="H60" t="n">
         <v>1381</v>
@@ -2138,7 +2138,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G61" t="n">
-        <v>2.53042459487915</v>
+        <v>2.53042435646057</v>
       </c>
       <c r="H61" t="n">
         <v>14026</v>
@@ -2515,7 +2515,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>2.81158304214478</v>
+        <v>2.8115828037262</v>
       </c>
       <c r="H74" t="n">
         <v>20161</v>
@@ -2544,7 +2544,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H75" t="n">
         <v>41308</v>
@@ -2573,7 +2573,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.88914394378662</v>
+        <v>2.88914370536804</v>
       </c>
       <c r="H76" t="n">
         <v>7786</v>
@@ -2602,7 +2602,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H77" t="n">
         <v>1600</v>
@@ -2805,7 +2805,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>2.9570095539093</v>
+        <v>2.95700931549072</v>
       </c>
       <c r="H84" t="n">
         <v>7079</v>
@@ -2921,7 +2921,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.03457045555115</v>
+        <v>3.03457069396973</v>
       </c>
       <c r="H88" t="n">
         <v>37120</v>
@@ -2950,7 +2950,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G89" t="n">
-        <v>3.09274125099182</v>
+        <v>3.09274101257324</v>
       </c>
       <c r="H89" t="n">
         <v>2382</v>
@@ -2979,7 +2979,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.21877765655518</v>
+        <v>3.2187774181366</v>
       </c>
       <c r="H90" t="n">
         <v>14770</v>
@@ -3008,7 +3008,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3545093536377</v>
+        <v>3.35450911521912</v>
       </c>
       <c r="H91" t="n">
         <v>19914</v>
@@ -3124,7 +3124,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>3.53871631622314</v>
+        <v>3.53871655464172</v>
       </c>
       <c r="H95" t="n">
         <v>10830</v>
@@ -3269,7 +3269,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H100" t="n">
         <v>6418</v>
@@ -3298,7 +3298,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H101" t="n">
         <v>8677</v>
@@ -3327,7 +3327,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H102" t="n">
         <v>2458</v>
@@ -3356,7 +3356,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>3.13152146339417</v>
+        <v>3.13152170181274</v>
       </c>
       <c r="H103" t="n">
         <v>3214</v>
@@ -3443,7 +3443,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.17030191421509</v>
+        <v>3.17030215263367</v>
       </c>
       <c r="H106" t="n">
         <v>9695</v>
@@ -3530,7 +3530,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G109" t="n">
-        <v>3.21877765655518</v>
+        <v>3.2187774181366</v>
       </c>
       <c r="H109" t="n">
         <v>9752</v>
@@ -3646,7 +3646,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>3.3545093536377</v>
+        <v>3.35450911521912</v>
       </c>
       <c r="H113" t="n">
         <v>1800</v>
@@ -3849,7 +3849,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>3.03457045555115</v>
+        <v>3.03457069396973</v>
       </c>
       <c r="H120" t="n">
         <v>1575</v>
@@ -3994,7 +3994,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G125" t="n">
-        <v>2.97639966011047</v>
+        <v>2.97639989852905</v>
       </c>
       <c r="H125" t="n">
         <v>1040</v>
@@ -4197,7 +4197,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H132" t="n">
         <v>13414</v>
@@ -4226,7 +4226,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H133" t="n">
         <v>3706</v>
@@ -4255,7 +4255,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>3.12182641029358</v>
+        <v>3.12182664871216</v>
       </c>
       <c r="H134" t="n">
         <v>16322</v>
@@ -4371,7 +4371,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>3.38359451293945</v>
+        <v>3.38359475135803</v>
       </c>
       <c r="H138" t="n">
         <v>940</v>
@@ -4400,7 +4400,7 @@
         <v>3.5</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39328956604004</v>
+        <v>3.39328980445862</v>
       </c>
       <c r="H139" t="n">
         <v>2713</v>
@@ -4429,7 +4429,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>3.199387550354</v>
+        <v>3.19938731193542</v>
       </c>
       <c r="H140" t="n">
         <v>25810</v>
@@ -4458,7 +4458,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G141" t="n">
-        <v>3.20908260345459</v>
+        <v>3.20908236503601</v>
       </c>
       <c r="H141" t="n">
         <v>9273</v>
@@ -4545,7 +4545,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G144" t="n">
-        <v>3.49993586540222</v>
+        <v>3.49993562698364</v>
       </c>
       <c r="H144" t="n">
         <v>7336</v>
@@ -4603,7 +4603,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>3.77139925956726</v>
+        <v>3.77139902114868</v>
       </c>
       <c r="H146" t="n">
         <v>19888</v>
@@ -5038,7 +5038,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>3.53871631622314</v>
+        <v>3.53871655464172</v>
       </c>
       <c r="H161" t="n">
         <v>11143</v>
@@ -5212,7 +5212,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G167" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H167" t="n">
         <v>19000</v>
@@ -5241,7 +5241,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H168" t="n">
         <v>8306</v>
@@ -5270,7 +5270,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G169" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H169" t="n">
         <v>4558</v>
@@ -5299,7 +5299,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H170" t="n">
         <v>2890</v>
@@ -5357,7 +5357,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H172" t="n">
         <v>3021</v>
@@ -5386,7 +5386,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H173" t="n">
         <v>502</v>
@@ -5531,7 +5531,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H178" t="n">
         <v>193</v>
@@ -5560,7 +5560,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G179" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H179" t="n">
         <v>200</v>
@@ -5705,7 +5705,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G184" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H184" t="n">
         <v>2570</v>
@@ -5821,7 +5821,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H188" t="n">
         <v>1553</v>
@@ -5850,7 +5850,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H189" t="n">
         <v>253</v>
@@ -5908,7 +5908,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G191" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H191" t="n">
         <v>550</v>
@@ -5937,7 +5937,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G192" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H194" t="n">
         <v>41</v>
@@ -6024,7 +6024,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G195" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H211" t="n">
         <v>2362</v>
@@ -6517,7 +6517,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H212" t="n">
         <v>2144</v>
@@ -6633,7 +6633,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G216" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H216" t="n">
         <v>1433</v>
@@ -6662,7 +6662,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>3.9653012752533</v>
+        <v>3.96530151367188</v>
       </c>
       <c r="H217" t="n">
         <v>152</v>
@@ -6691,7 +6691,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H218" t="n">
         <v>3009</v>
@@ -6865,7 +6865,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H224" t="n">
         <v>1205</v>
@@ -6952,7 +6952,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H227" t="n">
         <v>3822</v>
@@ -6981,7 +6981,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14950895309448</v>
+        <v>4.14950847625732</v>
       </c>
       <c r="H228" t="n">
         <v>2020</v>
@@ -7010,7 +7010,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H229" t="n">
         <v>305</v>
@@ -7155,7 +7155,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G234" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H234" t="n">
         <v>2110</v>
@@ -7213,7 +7213,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H236" t="n">
         <v>90</v>
@@ -7242,7 +7242,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G237" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G248" t="n">
-        <v>3.98469185829163</v>
+        <v>3.98469161987305</v>
       </c>
       <c r="H248" t="n">
         <v>4805</v>
@@ -7619,7 +7619,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>4.00408220291138</v>
+        <v>4.00408172607422</v>
       </c>
       <c r="H250" t="n">
         <v>2563</v>
@@ -7648,7 +7648,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>4.10103321075439</v>
+        <v>4.10103273391724</v>
       </c>
       <c r="H251" t="n">
         <v>185</v>
@@ -7764,7 +7764,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H255" t="n">
         <v>2204</v>
@@ -7793,7 +7793,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G256" t="n">
-        <v>3.9653012752533</v>
+        <v>3.96530151367188</v>
       </c>
       <c r="H256" t="n">
         <v>195</v>
@@ -8083,7 +8083,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H266" t="n">
         <v>1603</v>
@@ -8315,7 +8315,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>4.41127681732178</v>
+        <v>4.41127634048462</v>
       </c>
       <c r="H274" t="n">
         <v>5038</v>
@@ -8373,7 +8373,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G276" t="n">
-        <v>4.14950895309448</v>
+        <v>4.14950847625732</v>
       </c>
       <c r="H276" t="n">
         <v>710</v>
@@ -8547,7 +8547,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>4.10103321075439</v>
+        <v>4.10103273391724</v>
       </c>
       <c r="H282" t="n">
         <v>22</v>
@@ -8663,7 +8663,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.75200891494751</v>
+        <v>3.75200867652893</v>
       </c>
       <c r="H286" t="n">
         <v>6650</v>
@@ -8721,7 +8721,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.57749676704407</v>
+        <v>3.57749700546265</v>
       </c>
       <c r="H288" t="n">
         <v>5343</v>
@@ -8808,7 +8808,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G291" t="n">
-        <v>3.58719182014465</v>
+        <v>3.58719205856323</v>
       </c>
       <c r="H291" t="n">
         <v>186</v>
@@ -8924,7 +8924,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G295" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H295" t="n">
         <v>44240</v>
@@ -8953,7 +8953,7 @@
         <v>3.75</v>
       </c>
       <c r="G296" t="n">
-        <v>3.63566756248474</v>
+        <v>3.63566732406616</v>
       </c>
       <c r="H296" t="n">
         <v>6774</v>
@@ -9156,7 +9156,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H303" t="n">
         <v>10</v>
@@ -9185,7 +9185,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G304" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H304" t="n">
         <v>400</v>
@@ -9243,7 +9243,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H306" t="n">
         <v>100</v>
@@ -9272,7 +9272,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H307" t="n">
         <v>351</v>
@@ -9301,7 +9301,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G308" t="n">
-        <v>3.76170420646667</v>
+        <v>3.7617039680481</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>4.25</v>
       </c>
       <c r="G319" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H319" t="n">
         <v>2346</v>
@@ -9678,7 +9678,7 @@
         <v>4.25</v>
       </c>
       <c r="G321" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H321" t="n">
         <v>400</v>
@@ -9736,7 +9736,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H323" t="n">
         <v>6156</v>
@@ -9765,7 +9765,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H324" t="n">
         <v>50</v>
@@ -9794,7 +9794,7 @@
         <v>4.25</v>
       </c>
       <c r="G325" t="n">
-        <v>4.12042331695557</v>
+        <v>4.12042284011841</v>
       </c>
       <c r="H325" t="n">
         <v>2225</v>
@@ -9852,7 +9852,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H327" t="n">
         <v>1291</v>
@@ -9997,7 +9997,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H332" t="n">
         <v>2176</v>
@@ -10026,7 +10026,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>4.32402038574219</v>
+        <v>4.32402086257935</v>
       </c>
       <c r="H333" t="n">
         <v>6947</v>
@@ -10055,7 +10055,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H334" t="n">
         <v>2850</v>
@@ -10084,7 +10084,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H335" t="n">
         <v>3330</v>
@@ -10142,7 +10142,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H337" t="n">
         <v>1250</v>
@@ -10171,7 +10171,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G338" t="n">
-        <v>4.30463027954102</v>
+        <v>4.30463075637817</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>4.45005702972412</v>
+        <v>4.45005750656128</v>
       </c>
       <c r="H340" t="n">
         <v>3657</v>
@@ -10490,7 +10490,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H349" t="n">
         <v>275</v>
@@ -10519,7 +10519,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H350" t="n">
         <v>1768</v>
@@ -10664,7 +10664,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>4.6148738861084</v>
+        <v>4.61487436294556</v>
       </c>
       <c r="H355" t="n">
         <v>6262</v>
@@ -10693,7 +10693,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.75060606002808</v>
+        <v>4.75060558319092</v>
       </c>
       <c r="H356" t="n">
         <v>4002</v>
@@ -10780,7 +10780,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G359" t="n">
-        <v>5.0608491897583</v>
+        <v>5.06084871292114</v>
       </c>
       <c r="H359" t="n">
         <v>11409</v>
@@ -10838,7 +10838,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>4.63426399230957</v>
+        <v>4.63426446914673</v>
       </c>
       <c r="H361" t="n">
         <v>2991</v>
@@ -10867,7 +10867,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>4.6148738861084</v>
+        <v>4.61487436294556</v>
       </c>
       <c r="H362" t="n">
         <v>2537</v>
@@ -10896,7 +10896,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>4.45005702972412</v>
+        <v>4.45005750656128</v>
       </c>
       <c r="H363" t="n">
         <v>4303</v>
@@ -11012,7 +11012,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G367" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H367" t="n">
         <v>3131</v>
@@ -11041,7 +11041,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>4.17859363555908</v>
+        <v>4.17859411239624</v>
       </c>
       <c r="H368" t="n">
         <v>3753</v>
@@ -11215,7 +11215,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>5.0996298789978</v>
+        <v>5.09962940216064</v>
       </c>
       <c r="H374" t="n">
         <v>7576</v>
@@ -11331,7 +11331,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>4.79908132553101</v>
+        <v>4.79908084869385</v>
       </c>
       <c r="H378" t="n">
         <v>15636</v>
@@ -11447,7 +11447,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.15920352935791</v>
+        <v>4.15920400619507</v>
       </c>
       <c r="H382" t="n">
         <v>13041</v>
@@ -11795,7 +11795,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>4.26585006713867</v>
+        <v>4.26584959030151</v>
       </c>
       <c r="H394" t="n">
         <v>3776</v>
@@ -11911,7 +11911,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.80048441886902</v>
+        <v>3.8004846572876</v>
       </c>
       <c r="H398" t="n">
         <v>5798</v>
@@ -12056,7 +12056,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>3.94591116905212</v>
+        <v>3.9459114074707</v>
       </c>
       <c r="H403" t="n">
         <v>4450</v>
@@ -12375,7 +12375,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G414" t="n">
-        <v>3.62597250938416</v>
+        <v>3.62597227096558</v>
       </c>
       <c r="H414" t="n">
         <v>7546</v>
@@ -12694,7 +12694,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.49993586540222</v>
+        <v>3.49993562698364</v>
       </c>
       <c r="H425" t="n">
         <v>2789</v>
@@ -12723,7 +12723,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G426" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H426" t="n">
         <v>497</v>
@@ -12752,7 +12752,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H427" t="n">
         <v>10783</v>
@@ -12781,7 +12781,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>3.52902126312256</v>
+        <v>3.52902150154114</v>
       </c>
       <c r="H428" t="n">
         <v>103683</v>
@@ -12810,7 +12810,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.63566756248474</v>
+        <v>3.63566732406616</v>
       </c>
       <c r="H429" t="n">
         <v>10263</v>
@@ -12897,7 +12897,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G432" t="n">
-        <v>3.77139925956726</v>
+        <v>3.77139902114868</v>
       </c>
       <c r="H432" t="n">
         <v>18537</v>
@@ -12926,7 +12926,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90713095664978</v>
+        <v>3.9071307182312</v>
       </c>
       <c r="H433" t="n">
         <v>7020</v>
@@ -13013,7 +13013,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G436" t="n">
-        <v>3.84895992279053</v>
+        <v>3.84896016120911</v>
       </c>
       <c r="H436" t="n">
         <v>3204</v>
@@ -13071,7 +13071,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.94591116905212</v>
+        <v>3.9459114074707</v>
       </c>
       <c r="H438" t="n">
         <v>7716</v>
@@ -13100,7 +13100,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G439" t="n">
-        <v>4.0137767791748</v>
+        <v>4.01377725601196</v>
       </c>
       <c r="H439" t="n">
         <v>1963</v>
@@ -22937,6 +22937,35 @@
         <v>6304</v>
       </c>
       <c r="I778" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="s">
+        <v>9</v>
+      </c>
+      <c r="B779" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C779" t="n">
+        <v>3.84999990463257</v>
+      </c>
+      <c r="D779" t="n">
+        <v>3.99000000953674</v>
+      </c>
+      <c r="E779" t="n">
+        <v>3.84999990463257</v>
+      </c>
+      <c r="F779" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="G779" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="H779" t="n">
+        <v>8286</v>
+      </c>
+      <c r="I779" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -22951,7 +22951,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="D779" t="n">
-        <v>3.99000000953674</v>
+        <v>4.11999988555908</v>
       </c>
       <c r="E779" t="n">
         <v>3.84999990463257</v>
@@ -22966,6 +22966,35 @@
         <v>8286</v>
       </c>
       <c r="I779" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="s">
+        <v>9</v>
+      </c>
+      <c r="B780" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C780" t="n">
+        <v>4.09000015258789</v>
+      </c>
+      <c r="D780" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="E780" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="F780" t="n">
+        <v>4</v>
+      </c>
+      <c r="G780" t="n">
+        <v>4</v>
+      </c>
+      <c r="H780" t="n">
+        <v>7561</v>
+      </c>
+      <c r="I780" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -22980,7 +22980,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="D780" t="n">
-        <v>4.09999990463257</v>
+        <v>4.11999988555908</v>
       </c>
       <c r="E780" t="n">
         <v>3.92000007629395</v>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -22998,6 +22998,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="781">
+      <c r="A781" t="s">
+        <v>9</v>
+      </c>
+      <c r="B781" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C781" t="n">
+        <v>4</v>
+      </c>
+      <c r="D781" t="n">
+        <v>4</v>
+      </c>
+      <c r="E781" t="n">
+        <v>4</v>
+      </c>
+      <c r="F781" t="n">
+        <v>4</v>
+      </c>
+      <c r="G781" t="n">
+        <v>4</v>
+      </c>
+      <c r="H781" t="n">
+        <v>0</v>
+      </c>
+      <c r="I781" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="s">
+        <v>9</v>
+      </c>
+      <c r="B782" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C782" t="n">
+        <v>4.07000017166138</v>
+      </c>
+      <c r="D782" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="E782" t="n">
+        <v>3.98000001907349</v>
+      </c>
+      <c r="F782" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="G782" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="H782" t="n">
+        <v>4178</v>
+      </c>
+      <c r="I782" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -23056,6 +23056,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="783">
+      <c r="A783" t="s">
+        <v>9</v>
+      </c>
+      <c r="B783" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C783" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="D783" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="E783" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="F783" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="G783" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="H783" t="n">
+        <v>40</v>
+      </c>
+      <c r="I783" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G3" t="n">
-        <v>2.40923547744751</v>
+        <v>2.40923571586609</v>
       </c>
       <c r="H3" t="n">
         <v>24435</v>
@@ -949,7 +949,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46740627288818</v>
+        <v>2.46740651130676</v>
       </c>
       <c r="H20" t="n">
         <v>120</v>
@@ -1036,7 +1036,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.47710132598877</v>
+        <v>2.47710156440735</v>
       </c>
       <c r="H23" t="n">
         <v>500</v>
@@ -1152,7 +1152,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54011940956116</v>
+        <v>2.54011964797974</v>
       </c>
       <c r="H27" t="n">
         <v>3600</v>
@@ -1326,7 +1326,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4577112197876</v>
+        <v>2.45771145820618</v>
       </c>
       <c r="H33" t="n">
         <v>643</v>
@@ -1384,7 +1384,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H35" t="n">
         <v>16336</v>
@@ -1471,7 +1471,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>2.40438795089722</v>
+        <v>2.4043881893158</v>
       </c>
       <c r="H38" t="n">
         <v>2500</v>
@@ -1500,7 +1500,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.37530279159546</v>
+        <v>2.37530303001404</v>
       </c>
       <c r="H39" t="n">
         <v>10844</v>
@@ -1529,7 +1529,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>2.30743718147278</v>
+        <v>2.3074369430542</v>
       </c>
       <c r="H40" t="n">
         <v>9875</v>
@@ -1558,7 +1558,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.37530279159546</v>
+        <v>2.37530303001404</v>
       </c>
       <c r="H41" t="n">
         <v>5467</v>
@@ -1790,7 +1790,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H49" t="n">
         <v>1601</v>
@@ -1877,7 +1877,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.48194885253906</v>
+        <v>2.48194909095764</v>
       </c>
       <c r="H52" t="n">
         <v>3895</v>
@@ -1935,7 +1935,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>2.56920528411865</v>
+        <v>2.56920504570007</v>
       </c>
       <c r="H54" t="n">
         <v>626</v>
@@ -1964,7 +1964,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G55" t="n">
-        <v>2.54981470108032</v>
+        <v>2.5498149394989</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -2051,7 +2051,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>2.54011940956116</v>
+        <v>2.54011964797974</v>
       </c>
       <c r="H58" t="n">
         <v>9659</v>
@@ -2109,7 +2109,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>2.62737584114075</v>
+        <v>2.62737560272217</v>
       </c>
       <c r="H60" t="n">
         <v>1381</v>
@@ -2138,7 +2138,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G61" t="n">
-        <v>2.53042435646057</v>
+        <v>2.53042459487915</v>
       </c>
       <c r="H61" t="n">
         <v>14026</v>
@@ -2515,7 +2515,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8115828037262</v>
+        <v>2.81158304214478</v>
       </c>
       <c r="H74" t="n">
         <v>20161</v>
@@ -2544,7 +2544,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H75" t="n">
         <v>41308</v>
@@ -2573,7 +2573,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.88914370536804</v>
+        <v>2.88914394378662</v>
       </c>
       <c r="H76" t="n">
         <v>7786</v>
@@ -2602,7 +2602,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H77" t="n">
         <v>1600</v>
@@ -2805,7 +2805,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>2.95700931549072</v>
+        <v>2.9570095539093</v>
       </c>
       <c r="H84" t="n">
         <v>7079</v>
@@ -2921,7 +2921,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.03457069396973</v>
+        <v>3.03457045555115</v>
       </c>
       <c r="H88" t="n">
         <v>37120</v>
@@ -2950,7 +2950,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G89" t="n">
-        <v>3.09274101257324</v>
+        <v>3.09274125099182</v>
       </c>
       <c r="H89" t="n">
         <v>2382</v>
@@ -2979,7 +2979,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.2187774181366</v>
+        <v>3.21877765655518</v>
       </c>
       <c r="H90" t="n">
         <v>14770</v>
@@ -3008,7 +3008,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.35450911521912</v>
+        <v>3.3545093536377</v>
       </c>
       <c r="H91" t="n">
         <v>19914</v>
@@ -3124,7 +3124,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>3.53871655464172</v>
+        <v>3.53871631622314</v>
       </c>
       <c r="H95" t="n">
         <v>10830</v>
@@ -3269,7 +3269,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H100" t="n">
         <v>6418</v>
@@ -3298,7 +3298,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H101" t="n">
         <v>8677</v>
@@ -3327,7 +3327,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H102" t="n">
         <v>2458</v>
@@ -3356,7 +3356,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>3.13152170181274</v>
+        <v>3.13152146339417</v>
       </c>
       <c r="H103" t="n">
         <v>3214</v>
@@ -3443,7 +3443,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.17030215263367</v>
+        <v>3.17030191421509</v>
       </c>
       <c r="H106" t="n">
         <v>9695</v>
@@ -3530,7 +3530,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G109" t="n">
-        <v>3.2187774181366</v>
+        <v>3.21877765655518</v>
       </c>
       <c r="H109" t="n">
         <v>9752</v>
@@ -3646,7 +3646,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>3.35450911521912</v>
+        <v>3.3545093536377</v>
       </c>
       <c r="H113" t="n">
         <v>1800</v>
@@ -3849,7 +3849,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>3.03457069396973</v>
+        <v>3.03457045555115</v>
       </c>
       <c r="H120" t="n">
         <v>1575</v>
@@ -3994,7 +3994,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G125" t="n">
-        <v>2.97639989852905</v>
+        <v>2.97639966011047</v>
       </c>
       <c r="H125" t="n">
         <v>1040</v>
@@ -4197,7 +4197,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H132" t="n">
         <v>13414</v>
@@ -4226,7 +4226,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H133" t="n">
         <v>3706</v>
@@ -4255,7 +4255,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>3.12182664871216</v>
+        <v>3.12182641029358</v>
       </c>
       <c r="H134" t="n">
         <v>16322</v>
@@ -4371,7 +4371,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>3.38359475135803</v>
+        <v>3.38359451293945</v>
       </c>
       <c r="H138" t="n">
         <v>940</v>
@@ -4400,7 +4400,7 @@
         <v>3.5</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39328980445862</v>
+        <v>3.39328956604004</v>
       </c>
       <c r="H139" t="n">
         <v>2713</v>
@@ -4429,7 +4429,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>3.19938731193542</v>
+        <v>3.199387550354</v>
       </c>
       <c r="H140" t="n">
         <v>25810</v>
@@ -4458,7 +4458,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G141" t="n">
-        <v>3.20908236503601</v>
+        <v>3.20908260345459</v>
       </c>
       <c r="H141" t="n">
         <v>9273</v>
@@ -4545,7 +4545,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G144" t="n">
-        <v>3.49993562698364</v>
+        <v>3.49993586540222</v>
       </c>
       <c r="H144" t="n">
         <v>7336</v>
@@ -4603,7 +4603,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G146" t="n">
-        <v>3.77139902114868</v>
+        <v>3.77139925956726</v>
       </c>
       <c r="H146" t="n">
         <v>19888</v>
@@ -5038,7 +5038,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>3.53871655464172</v>
+        <v>3.53871631622314</v>
       </c>
       <c r="H161" t="n">
         <v>11143</v>
@@ -5212,7 +5212,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G167" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H167" t="n">
         <v>19000</v>
@@ -5241,7 +5241,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H168" t="n">
         <v>8306</v>
@@ -5270,7 +5270,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G169" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H169" t="n">
         <v>4558</v>
@@ -5299,7 +5299,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H170" t="n">
         <v>2890</v>
@@ -5357,7 +5357,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H172" t="n">
         <v>3021</v>
@@ -5386,7 +5386,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H173" t="n">
         <v>502</v>
@@ -5531,7 +5531,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H178" t="n">
         <v>193</v>
@@ -5560,7 +5560,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G179" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H179" t="n">
         <v>200</v>
@@ -5705,7 +5705,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G184" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H184" t="n">
         <v>2570</v>
@@ -5821,7 +5821,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H188" t="n">
         <v>1553</v>
@@ -5850,7 +5850,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H189" t="n">
         <v>253</v>
@@ -5908,7 +5908,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G191" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H191" t="n">
         <v>550</v>
@@ -5937,7 +5937,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G192" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H194" t="n">
         <v>41</v>
@@ -6024,7 +6024,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G195" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H211" t="n">
         <v>2362</v>
@@ -6517,7 +6517,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H212" t="n">
         <v>2144</v>
@@ -6633,7 +6633,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G216" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H216" t="n">
         <v>1433</v>
@@ -6662,7 +6662,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>3.96530151367188</v>
+        <v>3.9653012752533</v>
       </c>
       <c r="H217" t="n">
         <v>152</v>
@@ -6691,7 +6691,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H218" t="n">
         <v>3009</v>
@@ -6865,7 +6865,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H224" t="n">
         <v>1205</v>
@@ -6952,7 +6952,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H227" t="n">
         <v>3822</v>
@@ -6981,7 +6981,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14950847625732</v>
+        <v>4.14950895309448</v>
       </c>
       <c r="H228" t="n">
         <v>2020</v>
@@ -7010,7 +7010,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H229" t="n">
         <v>305</v>
@@ -7155,7 +7155,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G234" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H234" t="n">
         <v>2110</v>
@@ -7213,7 +7213,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H236" t="n">
         <v>90</v>
@@ -7242,7 +7242,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G237" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G238" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G248" t="n">
-        <v>3.98469161987305</v>
+        <v>3.98469185829163</v>
       </c>
       <c r="H248" t="n">
         <v>4805</v>
@@ -7619,7 +7619,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>4.00408172607422</v>
+        <v>4.00408220291138</v>
       </c>
       <c r="H250" t="n">
         <v>2563</v>
@@ -7648,7 +7648,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>4.10103273391724</v>
+        <v>4.10103321075439</v>
       </c>
       <c r="H251" t="n">
         <v>185</v>
@@ -7764,7 +7764,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H255" t="n">
         <v>2204</v>
@@ -7793,7 +7793,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G256" t="n">
-        <v>3.96530151367188</v>
+        <v>3.9653012752533</v>
       </c>
       <c r="H256" t="n">
         <v>195</v>
@@ -8083,7 +8083,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H266" t="n">
         <v>1603</v>
@@ -8315,7 +8315,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>4.41127634048462</v>
+        <v>4.41127681732178</v>
       </c>
       <c r="H274" t="n">
         <v>5038</v>
@@ -8373,7 +8373,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G276" t="n">
-        <v>4.14950847625732</v>
+        <v>4.14950895309448</v>
       </c>
       <c r="H276" t="n">
         <v>710</v>
@@ -8547,7 +8547,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>4.10103273391724</v>
+        <v>4.10103321075439</v>
       </c>
       <c r="H282" t="n">
         <v>22</v>
@@ -8663,7 +8663,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.75200867652893</v>
+        <v>3.75200891494751</v>
       </c>
       <c r="H286" t="n">
         <v>6650</v>
@@ -8721,7 +8721,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.57749700546265</v>
+        <v>3.57749676704407</v>
       </c>
       <c r="H288" t="n">
         <v>5343</v>
@@ -8808,7 +8808,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G291" t="n">
-        <v>3.58719205856323</v>
+        <v>3.58719182014465</v>
       </c>
       <c r="H291" t="n">
         <v>186</v>
@@ -8924,7 +8924,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G295" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H295" t="n">
         <v>44240</v>
@@ -8953,7 +8953,7 @@
         <v>3.75</v>
       </c>
       <c r="G296" t="n">
-        <v>3.63566732406616</v>
+        <v>3.63566756248474</v>
       </c>
       <c r="H296" t="n">
         <v>6774</v>
@@ -9156,7 +9156,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G303" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H303" t="n">
         <v>10</v>
@@ -9185,7 +9185,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G304" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H304" t="n">
         <v>400</v>
@@ -9243,7 +9243,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H306" t="n">
         <v>100</v>
@@ -9272,7 +9272,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H307" t="n">
         <v>351</v>
@@ -9301,7 +9301,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G308" t="n">
-        <v>3.7617039680481</v>
+        <v>3.76170420646667</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>4.25</v>
       </c>
       <c r="G319" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H319" t="n">
         <v>2346</v>
@@ -9678,7 +9678,7 @@
         <v>4.25</v>
       </c>
       <c r="G321" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H321" t="n">
         <v>400</v>
@@ -9736,7 +9736,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H323" t="n">
         <v>6156</v>
@@ -9765,7 +9765,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H324" t="n">
         <v>50</v>
@@ -9794,7 +9794,7 @@
         <v>4.25</v>
       </c>
       <c r="G325" t="n">
-        <v>4.12042284011841</v>
+        <v>4.12042331695557</v>
       </c>
       <c r="H325" t="n">
         <v>2225</v>
@@ -9852,7 +9852,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H327" t="n">
         <v>1291</v>
@@ -9997,7 +9997,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H332" t="n">
         <v>2176</v>
@@ -10026,7 +10026,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>4.32402086257935</v>
+        <v>4.32402038574219</v>
       </c>
       <c r="H333" t="n">
         <v>6947</v>
@@ -10055,7 +10055,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H334" t="n">
         <v>2850</v>
@@ -10084,7 +10084,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H335" t="n">
         <v>3330</v>
@@ -10142,7 +10142,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H337" t="n">
         <v>1250</v>
@@ -10171,7 +10171,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G338" t="n">
-        <v>4.30463075637817</v>
+        <v>4.30463027954102</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G340" t="n">
-        <v>4.45005750656128</v>
+        <v>4.45005702972412</v>
       </c>
       <c r="H340" t="n">
         <v>3657</v>
@@ -10490,7 +10490,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G349" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H349" t="n">
         <v>275</v>
@@ -10519,7 +10519,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H350" t="n">
         <v>1768</v>
@@ -10664,7 +10664,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G355" t="n">
-        <v>4.61487436294556</v>
+        <v>4.6148738861084</v>
       </c>
       <c r="H355" t="n">
         <v>6262</v>
@@ -10693,7 +10693,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.75060558319092</v>
+        <v>4.75060606002808</v>
       </c>
       <c r="H356" t="n">
         <v>4002</v>
@@ -10780,7 +10780,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G359" t="n">
-        <v>5.06084871292114</v>
+        <v>5.0608491897583</v>
       </c>
       <c r="H359" t="n">
         <v>11409</v>
@@ -10838,7 +10838,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>4.63426446914673</v>
+        <v>4.63426399230957</v>
       </c>
       <c r="H361" t="n">
         <v>2991</v>
@@ -10867,7 +10867,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>4.61487436294556</v>
+        <v>4.6148738861084</v>
       </c>
       <c r="H362" t="n">
         <v>2537</v>
@@ -10896,7 +10896,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>4.45005750656128</v>
+        <v>4.45005702972412</v>
       </c>
       <c r="H363" t="n">
         <v>4303</v>
@@ -11012,7 +11012,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G367" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H367" t="n">
         <v>3131</v>
@@ -11041,7 +11041,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>4.17859411239624</v>
+        <v>4.17859363555908</v>
       </c>
       <c r="H368" t="n">
         <v>3753</v>
@@ -11215,7 +11215,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>5.09962940216064</v>
+        <v>5.0996298789978</v>
       </c>
       <c r="H374" t="n">
         <v>7576</v>
@@ -11331,7 +11331,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>4.79908084869385</v>
+        <v>4.79908132553101</v>
       </c>
       <c r="H378" t="n">
         <v>15636</v>
@@ -11447,7 +11447,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.15920400619507</v>
+        <v>4.15920352935791</v>
       </c>
       <c r="H382" t="n">
         <v>13041</v>
@@ -11795,7 +11795,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>4.26584959030151</v>
+        <v>4.26585006713867</v>
       </c>
       <c r="H394" t="n">
         <v>3776</v>
@@ -11911,7 +11911,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.8004846572876</v>
+        <v>3.80048441886902</v>
       </c>
       <c r="H398" t="n">
         <v>5798</v>
@@ -12056,7 +12056,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>3.9459114074707</v>
+        <v>3.94591116905212</v>
       </c>
       <c r="H403" t="n">
         <v>4450</v>
@@ -12375,7 +12375,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G414" t="n">
-        <v>3.62597227096558</v>
+        <v>3.62597250938416</v>
       </c>
       <c r="H414" t="n">
         <v>7546</v>
@@ -12694,7 +12694,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G425" t="n">
-        <v>3.49993562698364</v>
+        <v>3.49993586540222</v>
       </c>
       <c r="H425" t="n">
         <v>2789</v>
@@ -12723,7 +12723,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G426" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H426" t="n">
         <v>497</v>
@@ -12752,7 +12752,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H427" t="n">
         <v>10783</v>
@@ -12781,7 +12781,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G428" t="n">
-        <v>3.52902150154114</v>
+        <v>3.52902126312256</v>
       </c>
       <c r="H428" t="n">
         <v>103683</v>
@@ -12810,7 +12810,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.63566732406616</v>
+        <v>3.63566756248474</v>
       </c>
       <c r="H429" t="n">
         <v>10263</v>
@@ -12897,7 +12897,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G432" t="n">
-        <v>3.77139902114868</v>
+        <v>3.77139925956726</v>
       </c>
       <c r="H432" t="n">
         <v>18537</v>
@@ -12926,7 +12926,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>3.9071307182312</v>
+        <v>3.90713095664978</v>
       </c>
       <c r="H433" t="n">
         <v>7020</v>
@@ -13013,7 +13013,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G436" t="n">
-        <v>3.84896016120911</v>
+        <v>3.84895992279053</v>
       </c>
       <c r="H436" t="n">
         <v>3204</v>
@@ -13071,7 +13071,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.9459114074707</v>
+        <v>3.94591116905212</v>
       </c>
       <c r="H438" t="n">
         <v>7716</v>
@@ -13100,7 +13100,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G439" t="n">
-        <v>4.01377725601196</v>
+        <v>4.0137767791748</v>
       </c>
       <c r="H439" t="n">
         <v>1963</v>
@@ -23082,6 +23082,35 @@
         <v>40</v>
       </c>
       <c r="I783" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="s">
+        <v>9</v>
+      </c>
+      <c r="B784" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C784" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="D784" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="E784" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="F784" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="G784" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="H784" t="n">
+        <v>8062</v>
+      </c>
+      <c r="I784" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ESF.MI.xlsx
+++ b/data/ESF.MI.xlsx
@@ -23114,6 +23114,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="785">
+      <c r="A785" t="s">
+        <v>9</v>
+      </c>
+      <c r="B785" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C785" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="D785" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="E785" t="n">
+        <v>4.05999994277954</v>
+      </c>
+      <c r="F785" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="G785" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="H785" t="n">
+        <v>6786</v>
+      </c>
+      <c r="I785" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
